--- a/research/traditional_assets/database/data/hungary/hungary_publishing_newspapers.xlsx
+++ b/research/traditional_assets/database/data/hungary/hungary_publishing_newspapers.xlsx
@@ -1278,7 +1278,7 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:Z101"/>
+  <dimension ref="A1:Z100"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" s="1" customFormat="1">
@@ -1415,22 +1415,22 @@
     </row>
     <row r="2">
       <c r="A2">
-        <v>0</v>
+        <v>0.01</v>
       </c>
       <c r="B2">
-        <v>0.1131338539393098</v>
+        <v>0.1130729834707644</v>
       </c>
       <c r="C2">
-        <v>186.7263914582291</v>
+        <v>185.0045248086496</v>
       </c>
       <c r="D2">
-        <v>162.2263914582291</v>
+        <v>162.3235248086496</v>
       </c>
       <c r="E2">
-        <v>-31.7</v>
+        <v>-29.881</v>
       </c>
       <c r="F2">
-        <v>0</v>
+        <v>1.819</v>
       </c>
       <c r="G2">
         <v>24.5</v>
@@ -1451,28 +1451,28 @@
         <v>28.6</v>
       </c>
       <c r="M2">
-        <v>0</v>
+        <v>0.09149569999999999</v>
       </c>
       <c r="N2">
-        <v>28.6</v>
+        <v>28.5085043</v>
       </c>
       <c r="O2">
-        <v>2.574</v>
+        <v>2.565765387</v>
       </c>
       <c r="P2">
-        <v>26.026</v>
+        <v>25.942738913</v>
       </c>
       <c r="Q2">
-        <v>32.126</v>
+        <v>32.04273891300001</v>
       </c>
       <c r="R2">
-        <v>0</v>
+        <v>0.0101010101010101</v>
       </c>
       <c r="S2">
-        <v>0.1131338539393098</v>
+        <v>0.1137527812836004</v>
       </c>
       <c r="T2">
-        <v>0.9797896186226994</v>
+        <v>0.9887957656221606</v>
       </c>
       <c r="U2">
         <v>0.0503</v>
@@ -1489,7 +1489,7 @@
         </is>
       </c>
       <c r="Y2">
-        <v>10000000</v>
+        <v>312.5829957036233</v>
       </c>
       <c r="Z2">
         <v>0</v>
@@ -1497,22 +1497,22 @@
     </row>
     <row r="3">
       <c r="A3">
-        <v>0.01</v>
+        <v>0.02</v>
       </c>
       <c r="B3">
-        <v>0.1130729834707644</v>
+        <v>0.1130121130022191</v>
       </c>
       <c r="C3">
-        <v>185.0045248086496</v>
+        <v>183.2827745463017</v>
       </c>
       <c r="D3">
-        <v>162.3235248086496</v>
+        <v>162.4207745463017</v>
       </c>
       <c r="E3">
-        <v>-29.881</v>
+        <v>-28.062</v>
       </c>
       <c r="F3">
-        <v>1.819</v>
+        <v>3.637999999999999</v>
       </c>
       <c r="G3">
         <v>24.5</v>
@@ -1533,28 +1533,28 @@
         <v>28.6</v>
       </c>
       <c r="M3">
-        <v>0.09149569999999999</v>
+        <v>0.1829914</v>
       </c>
       <c r="N3">
-        <v>28.5085043</v>
+        <v>28.4170086</v>
       </c>
       <c r="O3">
-        <v>2.565765387</v>
+        <v>2.557530774</v>
       </c>
       <c r="P3">
-        <v>25.942738913</v>
+        <v>25.859477826</v>
       </c>
       <c r="Q3">
-        <v>32.04273891300001</v>
+        <v>31.959477826</v>
       </c>
       <c r="R3">
-        <v>0.0101010101010101</v>
+        <v>0.02040816326530612</v>
       </c>
       <c r="S3">
-        <v>0.1137527812836004</v>
+        <v>0.1143843397981827</v>
       </c>
       <c r="T3">
-        <v>0.9887957656221606</v>
+        <v>0.9979857115399783</v>
       </c>
       <c r="U3">
         <v>0.0503</v>
@@ -1571,7 +1571,7 @@
         </is>
       </c>
       <c r="Y3">
-        <v>312.5829957036233</v>
+        <v>156.2914978518116</v>
       </c>
       <c r="Z3">
         <v>0</v>
@@ -1579,22 +1579,22 @@
     </row>
     <row r="4">
       <c r="A4">
-        <v>0.02</v>
+        <v>0.03</v>
       </c>
       <c r="B4">
-        <v>0.1130121130022191</v>
+        <v>0.1129512425336737</v>
       </c>
       <c r="C4">
-        <v>183.2827745463017</v>
+        <v>181.5611408804974</v>
       </c>
       <c r="D4">
-        <v>162.4207745463017</v>
+        <v>162.5181408804974</v>
       </c>
       <c r="E4">
-        <v>-28.062</v>
+        <v>-26.243</v>
       </c>
       <c r="F4">
-        <v>3.637999999999999</v>
+        <v>5.456999999999999</v>
       </c>
       <c r="G4">
         <v>24.5</v>
@@ -1615,28 +1615,28 @@
         <v>28.6</v>
       </c>
       <c r="M4">
-        <v>0.1829914</v>
+        <v>0.2744870999999999</v>
       </c>
       <c r="N4">
-        <v>28.4170086</v>
+        <v>28.3255129</v>
       </c>
       <c r="O4">
-        <v>2.557530774</v>
+        <v>2.549296161</v>
       </c>
       <c r="P4">
-        <v>25.859477826</v>
+        <v>25.776216739</v>
       </c>
       <c r="Q4">
-        <v>31.959477826</v>
+        <v>31.876216739</v>
       </c>
       <c r="R4">
-        <v>0.02040816326530612</v>
+        <v>0.03092783505154639</v>
       </c>
       <c r="S4">
-        <v>0.1143843397981827</v>
+        <v>0.1150289201378079</v>
       </c>
       <c r="T4">
-        <v>0.9979857115399783</v>
+        <v>1.007365140878782</v>
       </c>
       <c r="U4">
         <v>0.0503</v>
@@ -1653,7 +1653,7 @@
         </is>
       </c>
       <c r="Y4">
-        <v>156.2914978518116</v>
+        <v>104.1943319012078</v>
       </c>
       <c r="Z4">
         <v>0</v>
@@ -1661,22 +1661,22 @@
     </row>
     <row r="5">
       <c r="A5">
-        <v>0.03</v>
+        <v>0.04</v>
       </c>
       <c r="B5">
-        <v>0.1129512425336737</v>
+        <v>0.1128903720651283</v>
       </c>
       <c r="C5">
-        <v>181.5611408804974</v>
+        <v>179.8396240210508</v>
       </c>
       <c r="D5">
-        <v>162.5181408804974</v>
+        <v>162.6156240210508</v>
       </c>
       <c r="E5">
-        <v>-26.243</v>
+        <v>-24.424</v>
       </c>
       <c r="F5">
-        <v>5.456999999999999</v>
+        <v>7.275999999999999</v>
       </c>
       <c r="G5">
         <v>24.5</v>
@@ -1697,28 +1697,28 @@
         <v>28.6</v>
       </c>
       <c r="M5">
-        <v>0.2744870999999999</v>
+        <v>0.3659827999999999</v>
       </c>
       <c r="N5">
-        <v>28.3255129</v>
+        <v>28.2340172</v>
       </c>
       <c r="O5">
-        <v>2.549296161</v>
+        <v>2.541061548</v>
       </c>
       <c r="P5">
-        <v>25.776216739</v>
+        <v>25.692955652</v>
       </c>
       <c r="Q5">
-        <v>31.876216739</v>
+        <v>31.792955652</v>
       </c>
       <c r="R5">
-        <v>0.03092783505154639</v>
+        <v>0.04166666666666667</v>
       </c>
       <c r="S5">
-        <v>0.1150289201378079</v>
+        <v>0.1156869292345086</v>
       </c>
       <c r="T5">
-        <v>1.007365140878782</v>
+        <v>1.016939974995477</v>
       </c>
       <c r="U5">
         <v>0.0503</v>
@@ -1735,7 +1735,7 @@
         </is>
       </c>
       <c r="Y5">
-        <v>104.1943319012078</v>
+        <v>78.14574892590582</v>
       </c>
       <c r="Z5">
         <v>0</v>
@@ -1743,22 +1743,22 @@
     </row>
     <row r="6">
       <c r="A6">
-        <v>0.04</v>
+        <v>0.05</v>
       </c>
       <c r="B6">
-        <v>0.1128903720651283</v>
+        <v>0.1128295015965829</v>
       </c>
       <c r="C6">
-        <v>179.8396240210508</v>
+        <v>178.1182241782795</v>
       </c>
       <c r="D6">
-        <v>162.6156240210508</v>
+        <v>162.7132241782795</v>
       </c>
       <c r="E6">
-        <v>-24.424</v>
+        <v>-22.605</v>
       </c>
       <c r="F6">
-        <v>7.275999999999999</v>
+        <v>9.094999999999999</v>
       </c>
       <c r="G6">
         <v>24.5</v>
@@ -1779,28 +1779,28 @@
         <v>28.6</v>
       </c>
       <c r="M6">
-        <v>0.3659827999999999</v>
+        <v>0.4574784999999999</v>
       </c>
       <c r="N6">
-        <v>28.2340172</v>
+        <v>28.1425215</v>
       </c>
       <c r="O6">
-        <v>2.541061548</v>
+        <v>2.532826935</v>
       </c>
       <c r="P6">
-        <v>25.692955652</v>
+        <v>25.609694565</v>
       </c>
       <c r="Q6">
-        <v>31.792955652</v>
+        <v>31.709694565</v>
       </c>
       <c r="R6">
-        <v>0.04166666666666667</v>
+        <v>0.05263157894736843</v>
       </c>
       <c r="S6">
-        <v>0.1156869292345086</v>
+        <v>0.1163587911542978</v>
       </c>
       <c r="T6">
-        <v>1.016939974995477</v>
+        <v>1.02671638456726</v>
       </c>
       <c r="U6">
         <v>0.0503</v>
@@ -1817,7 +1817,7 @@
         </is>
       </c>
       <c r="Y6">
-        <v>78.14574892590582</v>
+        <v>62.51659914072467</v>
       </c>
       <c r="Z6">
         <v>0</v>
@@ -1825,22 +1825,22 @@
     </row>
     <row r="7">
       <c r="A7">
-        <v>0.05</v>
+        <v>0.06</v>
       </c>
       <c r="B7">
-        <v>0.1128295015965829</v>
+        <v>0.1127686311280375</v>
       </c>
       <c r="C7">
-        <v>178.1182241782795</v>
+        <v>176.3969415630066</v>
       </c>
       <c r="D7">
-        <v>162.7132241782795</v>
+        <v>162.8109415630066</v>
       </c>
       <c r="E7">
-        <v>-22.605</v>
+        <v>-20.786</v>
       </c>
       <c r="F7">
-        <v>9.094999999999999</v>
+        <v>10.914</v>
       </c>
       <c r="G7">
         <v>24.5</v>
@@ -1861,28 +1861,28 @@
         <v>28.6</v>
       </c>
       <c r="M7">
-        <v>0.4574784999999999</v>
+        <v>0.5489742</v>
       </c>
       <c r="N7">
-        <v>28.1425215</v>
+        <v>28.0510258</v>
       </c>
       <c r="O7">
-        <v>2.532826935</v>
+        <v>2.524592322</v>
       </c>
       <c r="P7">
-        <v>25.609694565</v>
+        <v>25.526433478</v>
       </c>
       <c r="Q7">
-        <v>31.709694565</v>
+        <v>31.626433478</v>
       </c>
       <c r="R7">
-        <v>0.05263157894736843</v>
+        <v>0.06382978723404256</v>
       </c>
       <c r="S7">
-        <v>0.1163587911542978</v>
+        <v>0.1170449480085506</v>
       </c>
       <c r="T7">
-        <v>1.02671638456726</v>
+        <v>1.036700802853337</v>
       </c>
       <c r="U7">
         <v>0.0503</v>
@@ -1899,7 +1899,7 @@
         </is>
       </c>
       <c r="Y7">
-        <v>62.51659914072467</v>
+        <v>52.09716595060388</v>
       </c>
       <c r="Z7">
         <v>0</v>
@@ -1907,22 +1907,22 @@
     </row>
     <row r="8">
       <c r="A8">
-        <v>0.06</v>
+        <v>0.06999999999999999</v>
       </c>
       <c r="B8">
-        <v>0.1127686311280375</v>
+        <v>0.1127077606594921</v>
       </c>
       <c r="C8">
-        <v>176.3969415630066</v>
+        <v>174.6757763865619</v>
       </c>
       <c r="D8">
-        <v>162.8109415630066</v>
+        <v>162.9087763865619</v>
       </c>
       <c r="E8">
-        <v>-20.786</v>
+        <v>-18.967</v>
       </c>
       <c r="F8">
-        <v>10.914</v>
+        <v>12.733</v>
       </c>
       <c r="G8">
         <v>24.5</v>
@@ -1943,28 +1943,28 @@
         <v>28.6</v>
       </c>
       <c r="M8">
-        <v>0.5489741999999999</v>
+        <v>0.6404698999999998</v>
       </c>
       <c r="N8">
-        <v>28.0510258</v>
+        <v>27.9595301</v>
       </c>
       <c r="O8">
-        <v>2.524592322</v>
+        <v>2.516357709</v>
       </c>
       <c r="P8">
-        <v>25.526433478</v>
+        <v>25.443172391</v>
       </c>
       <c r="Q8">
-        <v>31.626433478</v>
+        <v>31.543172391</v>
       </c>
       <c r="R8">
-        <v>0.06382978723404255</v>
+        <v>0.07526881720430106</v>
       </c>
       <c r="S8">
-        <v>0.1170449480085506</v>
+        <v>0.1177458609241851</v>
       </c>
       <c r="T8">
-        <v>1.036700802853337</v>
+        <v>1.046899939812233</v>
       </c>
       <c r="U8">
         <v>0.0503</v>
@@ -1981,7 +1981,7 @@
         </is>
       </c>
       <c r="Y8">
-        <v>52.09716595060389</v>
+        <v>44.65471367194619</v>
       </c>
       <c r="Z8">
         <v>0</v>
@@ -1989,22 +1989,22 @@
     </row>
     <row r="9">
       <c r="A9">
-        <v>0.07000000000000001</v>
+        <v>0.08</v>
       </c>
       <c r="B9">
-        <v>0.1127077606594922</v>
+        <v>0.1126468901909468</v>
       </c>
       <c r="C9">
-        <v>174.6757763865618</v>
+        <v>172.9547288607833</v>
       </c>
       <c r="D9">
-        <v>162.9087763865618</v>
+        <v>163.0067288607833</v>
       </c>
       <c r="E9">
-        <v>-18.967</v>
+        <v>-17.148</v>
       </c>
       <c r="F9">
-        <v>12.733</v>
+        <v>14.552</v>
       </c>
       <c r="G9">
         <v>24.5</v>
@@ -2025,28 +2025,28 @@
         <v>28.6</v>
       </c>
       <c r="M9">
-        <v>0.6404698999999999</v>
+        <v>0.7319655999999999</v>
       </c>
       <c r="N9">
-        <v>27.9595301</v>
+        <v>27.8680344</v>
       </c>
       <c r="O9">
-        <v>2.516357709</v>
+        <v>2.508123096</v>
       </c>
       <c r="P9">
-        <v>25.443172391</v>
+        <v>25.359911304</v>
       </c>
       <c r="Q9">
-        <v>31.543172391</v>
+        <v>31.459911304</v>
       </c>
       <c r="R9">
-        <v>0.07526881720430109</v>
+        <v>0.08695652173913043</v>
       </c>
       <c r="S9">
-        <v>0.1177458609241851</v>
+        <v>0.1184620110771161</v>
       </c>
       <c r="T9">
-        <v>1.046899939812233</v>
+        <v>1.0573207971398</v>
       </c>
       <c r="U9">
         <v>0.0503</v>
@@ -2063,7 +2063,7 @@
         </is>
       </c>
       <c r="Y9">
-        <v>44.65471367194618</v>
+        <v>39.07287446295291</v>
       </c>
       <c r="Z9">
         <v>0</v>
@@ -2071,22 +2071,22 @@
     </row>
     <row r="10">
       <c r="A10">
-        <v>0.08</v>
+        <v>0.09</v>
       </c>
       <c r="B10">
-        <v>0.1126468901909468</v>
+        <v>0.1125860197224014</v>
       </c>
       <c r="C10">
-        <v>172.9547288607833</v>
+        <v>171.2337991980186</v>
       </c>
       <c r="D10">
-        <v>163.0067288607833</v>
+        <v>163.1047991980186</v>
       </c>
       <c r="E10">
-        <v>-17.148</v>
+        <v>-15.329</v>
       </c>
       <c r="F10">
-        <v>14.552</v>
+        <v>16.371</v>
       </c>
       <c r="G10">
         <v>24.5</v>
@@ -2107,28 +2107,28 @@
         <v>28.6</v>
       </c>
       <c r="M10">
-        <v>0.7319655999999999</v>
+        <v>0.8234612999999998</v>
       </c>
       <c r="N10">
-        <v>27.8680344</v>
+        <v>27.7765387</v>
       </c>
       <c r="O10">
-        <v>2.508123096</v>
+        <v>2.499888483</v>
       </c>
       <c r="P10">
-        <v>25.359911304</v>
+        <v>25.276650217</v>
       </c>
       <c r="Q10">
-        <v>31.459911304</v>
+        <v>31.37665021700001</v>
       </c>
       <c r="R10">
-        <v>0.08695652173913043</v>
+        <v>0.0989010989010989</v>
       </c>
       <c r="S10">
-        <v>0.1184620110771161</v>
+        <v>0.1191939007938477</v>
       </c>
       <c r="T10">
-        <v>1.0573207971398</v>
+        <v>1.067970684298742</v>
       </c>
       <c r="U10">
         <v>0.0503</v>
@@ -2145,7 +2145,7 @@
         </is>
       </c>
       <c r="Y10">
-        <v>39.07287446295291</v>
+        <v>34.73144396706926</v>
       </c>
       <c r="Z10">
         <v>0</v>
@@ -2153,22 +2153,22 @@
     </row>
     <row r="11">
       <c r="A11">
-        <v>0.09</v>
+        <v>0.09999999999999999</v>
       </c>
       <c r="B11">
-        <v>0.1125860197224014</v>
+        <v>0.112525149253856</v>
       </c>
       <c r="C11">
-        <v>171.2337991980186</v>
+        <v>169.5129876111271</v>
       </c>
       <c r="D11">
-        <v>163.1047991980186</v>
+        <v>163.2029876111271</v>
       </c>
       <c r="E11">
-        <v>-15.329</v>
+        <v>-13.51</v>
       </c>
       <c r="F11">
-        <v>16.371</v>
+        <v>18.19</v>
       </c>
       <c r="G11">
         <v>24.5</v>
@@ -2189,28 +2189,28 @@
         <v>28.6</v>
       </c>
       <c r="M11">
-        <v>0.8234612999999998</v>
+        <v>0.9149569999999998</v>
       </c>
       <c r="N11">
-        <v>27.7765387</v>
+        <v>27.685043</v>
       </c>
       <c r="O11">
-        <v>2.499888483</v>
+        <v>2.49165387</v>
       </c>
       <c r="P11">
-        <v>25.276650217</v>
+        <v>25.19338913</v>
       </c>
       <c r="Q11">
-        <v>31.37665021700001</v>
+        <v>31.29338913</v>
       </c>
       <c r="R11">
-        <v>0.0989010989010989</v>
+        <v>0.1111111111111111</v>
       </c>
       <c r="S11">
-        <v>0.1191939007938477</v>
+        <v>0.1199420547265067</v>
       </c>
       <c r="T11">
-        <v>1.067970684298742</v>
+        <v>1.078857235616772</v>
       </c>
       <c r="U11">
         <v>0.0503</v>
@@ -2227,7 +2227,7 @@
         </is>
       </c>
       <c r="Y11">
-        <v>34.73144396706926</v>
+        <v>31.25829957036233</v>
       </c>
       <c r="Z11">
         <v>0</v>
@@ -2235,22 +2235,22 @@
     </row>
     <row r="12">
       <c r="A12">
-        <v>0.1</v>
+        <v>0.11</v>
       </c>
       <c r="B12">
-        <v>0.1125251492538561</v>
+        <v>0.1124642787853106</v>
       </c>
       <c r="C12">
-        <v>169.512987611127</v>
+        <v>167.7922943134807</v>
       </c>
       <c r="D12">
-        <v>163.202987611127</v>
+        <v>163.3012943134807</v>
       </c>
       <c r="E12">
-        <v>-13.51</v>
+        <v>-11.691</v>
       </c>
       <c r="F12">
-        <v>18.19</v>
+        <v>20.009</v>
       </c>
       <c r="G12">
         <v>24.5</v>
@@ -2271,28 +2271,28 @@
         <v>28.6</v>
       </c>
       <c r="M12">
-        <v>0.9149569999999998</v>
+        <v>1.0064527</v>
       </c>
       <c r="N12">
-        <v>27.685043</v>
+        <v>27.5935473</v>
       </c>
       <c r="O12">
-        <v>2.49165387</v>
+        <v>2.483419257</v>
       </c>
       <c r="P12">
-        <v>25.19338913</v>
+        <v>25.110128043</v>
       </c>
       <c r="Q12">
-        <v>31.29338913</v>
+        <v>31.210128043</v>
       </c>
       <c r="R12">
-        <v>0.1111111111111111</v>
+        <v>0.1235955056179775</v>
       </c>
       <c r="S12">
-        <v>0.1199420547265067</v>
+        <v>0.1207070211070906</v>
       </c>
       <c r="T12">
-        <v>1.078857235616772</v>
+        <v>1.089988428537455</v>
       </c>
       <c r="U12">
         <v>0.0503</v>
@@ -2309,7 +2309,7 @@
         </is>
       </c>
       <c r="Y12">
-        <v>31.25829957036233</v>
+        <v>28.41663597305666</v>
       </c>
       <c r="Z12">
         <v>0</v>
@@ -2317,22 +2317,22 @@
     </row>
     <row r="13">
       <c r="A13">
-        <v>0.11</v>
+        <v>0.12</v>
       </c>
       <c r="B13">
-        <v>0.1124642787853106</v>
+        <v>0.1124034083167653</v>
       </c>
       <c r="C13">
-        <v>167.7922943134807</v>
+        <v>166.0717195189658</v>
       </c>
       <c r="D13">
-        <v>163.3012943134807</v>
+        <v>163.3997195189658</v>
       </c>
       <c r="E13">
-        <v>-11.691</v>
+        <v>-9.872000000000003</v>
       </c>
       <c r="F13">
-        <v>20.009</v>
+        <v>21.828</v>
       </c>
       <c r="G13">
         <v>24.5</v>
@@ -2353,28 +2353,28 @@
         <v>28.6</v>
       </c>
       <c r="M13">
-        <v>1.0064527</v>
+        <v>1.0979484</v>
       </c>
       <c r="N13">
-        <v>27.5935473</v>
+        <v>27.5020516</v>
       </c>
       <c r="O13">
-        <v>2.483419257</v>
+        <v>2.475184644</v>
       </c>
       <c r="P13">
-        <v>25.110128043</v>
+        <v>25.026866956</v>
       </c>
       <c r="Q13">
-        <v>31.210128043</v>
+        <v>31.126866956</v>
       </c>
       <c r="R13">
-        <v>0.1235955056179775</v>
+        <v>0.1363636363636364</v>
       </c>
       <c r="S13">
-        <v>0.1207070211070906</v>
+        <v>0.1214893730872333</v>
       </c>
       <c r="T13">
-        <v>1.089988428537455</v>
+        <v>1.101372603115425</v>
       </c>
       <c r="U13">
         <v>0.0503</v>
@@ -2391,7 +2391,7 @@
         </is>
       </c>
       <c r="Y13">
-        <v>28.41663597305666</v>
+        <v>26.04858297530194</v>
       </c>
       <c r="Z13">
         <v>0</v>
@@ -2399,22 +2399,22 @@
     </row>
     <row r="14">
       <c r="A14">
-        <v>0.12</v>
+        <v>0.13</v>
       </c>
       <c r="B14">
-        <v>0.1124034083167653</v>
+        <v>0.1123425378482199</v>
       </c>
       <c r="C14">
-        <v>166.0717195189658</v>
+        <v>164.3512634419849</v>
       </c>
       <c r="D14">
-        <v>163.3997195189658</v>
+        <v>163.4982634419848</v>
       </c>
       <c r="E14">
-        <v>-9.872000000000003</v>
+        <v>-8.053000000000001</v>
       </c>
       <c r="F14">
-        <v>21.828</v>
+        <v>23.647</v>
       </c>
       <c r="G14">
         <v>24.5</v>
@@ -2435,28 +2435,28 @@
         <v>28.6</v>
       </c>
       <c r="M14">
-        <v>1.0979484</v>
+        <v>1.1894441</v>
       </c>
       <c r="N14">
-        <v>27.5020516</v>
+        <v>27.4105559</v>
       </c>
       <c r="O14">
-        <v>2.475184644</v>
+        <v>2.466950031</v>
       </c>
       <c r="P14">
-        <v>25.026866956</v>
+        <v>24.943605869</v>
       </c>
       <c r="Q14">
-        <v>31.126866956</v>
+        <v>31.043605869</v>
       </c>
       <c r="R14">
-        <v>0.1363636363636364</v>
+        <v>0.1494252873563219</v>
       </c>
       <c r="S14">
-        <v>0.1214893730872333</v>
+        <v>0.1222897101703677</v>
       </c>
       <c r="T14">
-        <v>1.101372603115425</v>
+        <v>1.113018482856108</v>
       </c>
       <c r="U14">
         <v>0.0503</v>
@@ -2473,7 +2473,7 @@
         </is>
       </c>
       <c r="Y14">
-        <v>26.04858297530194</v>
+        <v>24.04484582335564</v>
       </c>
       <c r="Z14">
         <v>0</v>
@@ -2481,22 +2481,22 @@
     </row>
     <row r="15">
       <c r="A15">
-        <v>0.13</v>
+        <v>0.14</v>
       </c>
       <c r="B15">
-        <v>0.1123425378482199</v>
+        <v>0.1122816673796745</v>
       </c>
       <c r="C15">
-        <v>164.3512634419849</v>
+        <v>162.6309262974577</v>
       </c>
       <c r="D15">
-        <v>163.4982634419848</v>
+        <v>163.5969262974577</v>
       </c>
       <c r="E15">
-        <v>-8.053000000000001</v>
+        <v>-6.234000000000002</v>
       </c>
       <c r="F15">
-        <v>23.647</v>
+        <v>25.466</v>
       </c>
       <c r="G15">
         <v>24.5</v>
@@ -2517,28 +2517,28 @@
         <v>28.6</v>
       </c>
       <c r="M15">
-        <v>1.1894441</v>
+        <v>1.2809398</v>
       </c>
       <c r="N15">
-        <v>27.4105559</v>
+        <v>27.3190602</v>
       </c>
       <c r="O15">
-        <v>2.466950031</v>
+        <v>2.458715418</v>
       </c>
       <c r="P15">
-        <v>24.943605869</v>
+        <v>24.860344782</v>
       </c>
       <c r="Q15">
-        <v>31.043605869</v>
+        <v>30.960344782</v>
       </c>
       <c r="R15">
-        <v>0.1494252873563219</v>
+        <v>0.1627906976744186</v>
       </c>
       <c r="S15">
-        <v>0.1222897101703677</v>
+        <v>0.1231086597438076</v>
       </c>
       <c r="T15">
-        <v>1.113018482856108</v>
+        <v>1.124935197009364</v>
       </c>
       <c r="U15">
         <v>0.0503</v>
@@ -2555,7 +2555,7 @@
         </is>
       </c>
       <c r="Y15">
-        <v>24.04484582335564</v>
+        <v>22.32735683597309</v>
       </c>
       <c r="Z15">
         <v>0</v>
@@ -2563,22 +2563,22 @@
     </row>
     <row r="16">
       <c r="A16">
-        <v>0.14</v>
+        <v>0.15</v>
       </c>
       <c r="B16">
-        <v>0.1122816673796745</v>
+        <v>0.1122207969111291</v>
       </c>
       <c r="C16">
-        <v>162.6309262974577</v>
+        <v>160.9107083008234</v>
       </c>
       <c r="D16">
-        <v>163.5969262974577</v>
+        <v>163.6957083008234</v>
       </c>
       <c r="E16">
-        <v>-6.234000000000002</v>
+        <v>-4.414999999999999</v>
       </c>
       <c r="F16">
-        <v>25.466</v>
+        <v>27.285</v>
       </c>
       <c r="G16">
         <v>24.5</v>
@@ -2599,28 +2599,28 @@
         <v>28.6</v>
       </c>
       <c r="M16">
-        <v>1.2809398</v>
+        <v>1.3724355</v>
       </c>
       <c r="N16">
-        <v>27.3190602</v>
+        <v>27.2275645</v>
       </c>
       <c r="O16">
-        <v>2.458715418</v>
+        <v>2.450480805</v>
       </c>
       <c r="P16">
-        <v>24.860344782</v>
+        <v>24.777083695</v>
       </c>
       <c r="Q16">
-        <v>30.960344782</v>
+        <v>30.877083695</v>
       </c>
       <c r="R16">
-        <v>0.1627906976744186</v>
+        <v>0.1764705882352942</v>
       </c>
       <c r="S16">
-        <v>0.1231086597438076</v>
+        <v>0.1239468787189754</v>
       </c>
       <c r="T16">
-        <v>1.124935197009364</v>
+        <v>1.137132304436815</v>
       </c>
       <c r="U16">
         <v>0.0503</v>
@@ -2637,7 +2637,7 @@
         </is>
       </c>
       <c r="Y16">
-        <v>22.32735683597309</v>
+        <v>20.83886638024155</v>
       </c>
       <c r="Z16">
         <v>0</v>
@@ -2645,22 +2645,22 @@
     </row>
     <row r="17">
       <c r="A17">
-        <v>0.15</v>
+        <v>0.16</v>
       </c>
       <c r="B17">
-        <v>0.1122207969111291</v>
+        <v>0.1121599264425838</v>
       </c>
       <c r="C17">
-        <v>160.9107083008234</v>
+        <v>159.1906096680416</v>
       </c>
       <c r="D17">
-        <v>163.6957083008234</v>
+        <v>163.7946096680416</v>
       </c>
       <c r="E17">
-        <v>-4.415000000000003</v>
+        <v>-2.596000000000004</v>
       </c>
       <c r="F17">
-        <v>27.285</v>
+        <v>29.104</v>
       </c>
       <c r="G17">
         <v>24.5</v>
@@ -2681,28 +2681,28 @@
         <v>28.6</v>
       </c>
       <c r="M17">
-        <v>1.3724355</v>
+        <v>1.4639312</v>
       </c>
       <c r="N17">
-        <v>27.2275645</v>
+        <v>27.1360688</v>
       </c>
       <c r="O17">
-        <v>2.450480805</v>
+        <v>2.442246192</v>
       </c>
       <c r="P17">
-        <v>24.777083695</v>
+        <v>24.693822608</v>
       </c>
       <c r="Q17">
-        <v>30.877083695</v>
+        <v>30.793822608</v>
       </c>
       <c r="R17">
-        <v>0.1764705882352941</v>
+        <v>0.1904761904761905</v>
       </c>
       <c r="S17">
-        <v>0.1239468787189754</v>
+        <v>0.1248050552887902</v>
       </c>
       <c r="T17">
-        <v>1.137132304436815</v>
+        <v>1.149619819183967</v>
       </c>
       <c r="U17">
         <v>0.0503</v>
@@ -2719,7 +2719,7 @@
         </is>
       </c>
       <c r="Y17">
-        <v>20.83886638024156</v>
+        <v>19.53643723147646</v>
       </c>
       <c r="Z17">
         <v>0</v>
@@ -2727,22 +2727,22 @@
     </row>
     <row r="18">
       <c r="A18">
-        <v>0.16</v>
+        <v>0.17</v>
       </c>
       <c r="B18">
-        <v>0.1121599264425838</v>
+        <v>0.1120990559740384</v>
       </c>
       <c r="C18">
-        <v>159.1906096680416</v>
+        <v>157.4706306155942</v>
       </c>
       <c r="D18">
-        <v>163.7946096680416</v>
+        <v>163.8936306155942</v>
       </c>
       <c r="E18">
-        <v>-2.596000000000004</v>
+        <v>-0.777000000000001</v>
       </c>
       <c r="F18">
-        <v>29.104</v>
+        <v>30.923</v>
       </c>
       <c r="G18">
         <v>24.5</v>
@@ -2763,28 +2763,28 @@
         <v>28.6</v>
       </c>
       <c r="M18">
-        <v>1.4639312</v>
+        <v>1.5554269</v>
       </c>
       <c r="N18">
-        <v>27.1360688</v>
+        <v>27.0445731</v>
       </c>
       <c r="O18">
-        <v>2.442246192</v>
+        <v>2.434011579</v>
       </c>
       <c r="P18">
-        <v>24.693822608</v>
+        <v>24.610561521</v>
       </c>
       <c r="Q18">
-        <v>30.793822608</v>
+        <v>30.710561521</v>
       </c>
       <c r="R18">
-        <v>0.1904761904761905</v>
+        <v>0.2048192771084338</v>
       </c>
       <c r="S18">
-        <v>0.1248050552887902</v>
+        <v>0.1256839108120944</v>
       </c>
       <c r="T18">
-        <v>1.149619819183967</v>
+        <v>1.16240823790093</v>
       </c>
       <c r="U18">
         <v>0.0503</v>
@@ -2801,7 +2801,7 @@
         </is>
       </c>
       <c r="Y18">
-        <v>19.53643723147646</v>
+        <v>18.38723504138961</v>
       </c>
       <c r="Z18">
         <v>0</v>
@@ -2809,22 +2809,22 @@
     </row>
     <row r="19">
       <c r="A19">
-        <v>0.17</v>
+        <v>0.18</v>
       </c>
       <c r="B19">
-        <v>0.1120990559740384</v>
+        <v>0.112038185505493</v>
       </c>
       <c r="C19">
-        <v>157.4706306155942</v>
+        <v>155.7507713604868</v>
       </c>
       <c r="D19">
-        <v>163.8936306155942</v>
+        <v>163.9927713604868</v>
       </c>
       <c r="E19">
-        <v>-0.777000000000001</v>
+        <v>1.041999999999998</v>
       </c>
       <c r="F19">
-        <v>30.923</v>
+        <v>32.742</v>
       </c>
       <c r="G19">
         <v>24.5</v>
@@ -2845,28 +2845,28 @@
         <v>28.6</v>
       </c>
       <c r="M19">
-        <v>1.5554269</v>
+        <v>1.6469226</v>
       </c>
       <c r="N19">
-        <v>27.0445731</v>
+        <v>26.9530774</v>
       </c>
       <c r="O19">
-        <v>2.434011579</v>
+        <v>2.425776966</v>
       </c>
       <c r="P19">
-        <v>24.610561521</v>
+        <v>24.527300434</v>
       </c>
       <c r="Q19">
-        <v>30.710561521</v>
+        <v>30.627300434</v>
       </c>
       <c r="R19">
-        <v>0.2048192771084338</v>
+        <v>0.2195121951219512</v>
       </c>
       <c r="S19">
-        <v>0.1256839108120944</v>
+        <v>0.1265842018359671</v>
       </c>
       <c r="T19">
-        <v>1.16240823790093</v>
+        <v>1.175508569269526</v>
       </c>
       <c r="U19">
         <v>0.0503</v>
@@ -2883,7 +2883,7 @@
         </is>
       </c>
       <c r="Y19">
-        <v>18.38723504138961</v>
+        <v>17.36572198353463</v>
       </c>
       <c r="Z19">
         <v>0</v>
@@ -2891,22 +2891,22 @@
     </row>
     <row r="20">
       <c r="A20">
-        <v>0.18</v>
+        <v>0.19</v>
       </c>
       <c r="B20">
-        <v>0.112038185505493</v>
+        <v>0.1119773150369476</v>
       </c>
       <c r="C20">
-        <v>155.7507713604868</v>
+        <v>154.0310321202506</v>
       </c>
       <c r="D20">
-        <v>163.9927713604868</v>
+        <v>164.0920321202506</v>
       </c>
       <c r="E20">
-        <v>1.041999999999998</v>
+        <v>2.860999999999994</v>
       </c>
       <c r="F20">
-        <v>32.742</v>
+        <v>34.56099999999999</v>
       </c>
       <c r="G20">
         <v>24.5</v>
@@ -2927,28 +2927,28 @@
         <v>28.6</v>
       </c>
       <c r="M20">
-        <v>1.6469226</v>
+        <v>1.7384183</v>
       </c>
       <c r="N20">
-        <v>26.9530774</v>
+        <v>26.8615817</v>
       </c>
       <c r="O20">
-        <v>2.425776966</v>
+        <v>2.417542353</v>
       </c>
       <c r="P20">
-        <v>24.527300434</v>
+        <v>24.444039347</v>
       </c>
       <c r="Q20">
-        <v>30.627300434</v>
+        <v>30.544039347</v>
       </c>
       <c r="R20">
-        <v>0.2195121951219512</v>
+        <v>0.2345679012345679</v>
       </c>
       <c r="S20">
-        <v>0.1265842018359671</v>
+        <v>0.1275067222678366</v>
       </c>
       <c r="T20">
-        <v>1.175508569269526</v>
+        <v>1.188932365610187</v>
       </c>
       <c r="U20">
         <v>0.0503</v>
@@ -2965,7 +2965,7 @@
         </is>
       </c>
       <c r="Y20">
-        <v>17.36572198353463</v>
+        <v>16.45173661598017</v>
       </c>
       <c r="Z20">
         <v>0</v>
@@ -2973,22 +2973,22 @@
     </row>
     <row r="21">
       <c r="A21">
-        <v>0.19</v>
+        <v>0.2</v>
       </c>
       <c r="B21">
-        <v>0.1119773150369476</v>
+        <v>0.1119164445684023</v>
       </c>
       <c r="C21">
-        <v>154.0310321202506</v>
+        <v>152.3114131129436</v>
       </c>
       <c r="D21">
-        <v>164.0920321202506</v>
+        <v>164.1914131129436</v>
       </c>
       <c r="E21">
-        <v>2.860999999999994</v>
+        <v>4.679999999999996</v>
       </c>
       <c r="F21">
-        <v>34.56099999999999</v>
+        <v>36.38</v>
       </c>
       <c r="G21">
         <v>24.5</v>
@@ -3009,28 +3009,28 @@
         <v>28.6</v>
       </c>
       <c r="M21">
-        <v>1.7384183</v>
+        <v>1.829914</v>
       </c>
       <c r="N21">
-        <v>26.8615817</v>
+        <v>26.770086</v>
       </c>
       <c r="O21">
-        <v>2.417542353</v>
+        <v>2.40930774</v>
       </c>
       <c r="P21">
-        <v>24.444039347</v>
+        <v>24.36077826</v>
       </c>
       <c r="Q21">
-        <v>30.544039347</v>
+        <v>30.46077826</v>
       </c>
       <c r="R21">
-        <v>0.2345679012345679</v>
+        <v>0.25</v>
       </c>
       <c r="S21">
-        <v>0.1275067222678366</v>
+        <v>0.1284523057105028</v>
       </c>
       <c r="T21">
-        <v>1.188932365610187</v>
+        <v>1.202691756859364</v>
       </c>
       <c r="U21">
         <v>0.0503</v>
@@ -3047,7 +3047,7 @@
         </is>
       </c>
       <c r="Y21">
-        <v>16.45173661598017</v>
+        <v>15.62914978518117</v>
       </c>
       <c r="Z21">
         <v>0</v>
@@ -3055,22 +3055,22 @@
     </row>
     <row r="22">
       <c r="A22">
-        <v>0.2</v>
+        <v>0.21</v>
       </c>
       <c r="B22">
-        <v>0.1119164445684023</v>
+        <v>0.1118555740998569</v>
       </c>
       <c r="C22">
-        <v>152.3114131129436</v>
+        <v>150.5919145571524</v>
       </c>
       <c r="D22">
-        <v>164.1914131129436</v>
+        <v>164.2909145571524</v>
       </c>
       <c r="E22">
-        <v>4.679999999999996</v>
+        <v>6.498999999999999</v>
       </c>
       <c r="F22">
-        <v>36.38</v>
+        <v>38.199</v>
       </c>
       <c r="G22">
         <v>24.5</v>
@@ -3091,28 +3091,28 @@
         <v>28.6</v>
       </c>
       <c r="M22">
-        <v>1.829914</v>
+        <v>1.9214097</v>
       </c>
       <c r="N22">
-        <v>26.770086</v>
+        <v>26.6785903</v>
       </c>
       <c r="O22">
-        <v>2.40930774</v>
+        <v>2.401073127</v>
       </c>
       <c r="P22">
-        <v>24.36077826</v>
+        <v>24.277517173</v>
       </c>
       <c r="Q22">
-        <v>30.46077826</v>
+        <v>30.377517173</v>
       </c>
       <c r="R22">
-        <v>0.25</v>
+        <v>0.2658227848101266</v>
       </c>
       <c r="S22">
-        <v>0.1284523057105028</v>
+        <v>0.1294218279745024</v>
       </c>
       <c r="T22">
-        <v>1.202691756859364</v>
+        <v>1.216799487127507</v>
       </c>
       <c r="U22">
         <v>0.0503</v>
@@ -3129,7 +3129,7 @@
         </is>
       </c>
       <c r="Y22">
-        <v>15.62914978518117</v>
+        <v>14.88490455731539</v>
       </c>
       <c r="Z22">
         <v>0</v>
@@ -3137,22 +3137,22 @@
     </row>
     <row r="23">
       <c r="A23">
-        <v>0.21</v>
+        <v>0.22</v>
       </c>
       <c r="B23">
-        <v>0.1118555740998569</v>
+        <v>0.1117947036313115</v>
       </c>
       <c r="C23">
-        <v>150.5919145571524</v>
+        <v>148.8725366719939</v>
       </c>
       <c r="D23">
-        <v>164.2909145571524</v>
+        <v>164.3905366719939</v>
       </c>
       <c r="E23">
-        <v>6.498999999999992</v>
+        <v>8.317999999999994</v>
       </c>
       <c r="F23">
-        <v>38.19899999999999</v>
+        <v>40.01799999999999</v>
       </c>
       <c r="G23">
         <v>24.5</v>
@@ -3173,28 +3173,28 @@
         <v>28.6</v>
       </c>
       <c r="M23">
-        <v>1.921409699999999</v>
+        <v>2.0129054</v>
       </c>
       <c r="N23">
-        <v>26.6785903</v>
+        <v>26.5870946</v>
       </c>
       <c r="O23">
-        <v>2.401073127</v>
+        <v>2.392838514</v>
       </c>
       <c r="P23">
-        <v>24.277517173</v>
+        <v>24.194256086</v>
       </c>
       <c r="Q23">
-        <v>30.377517173</v>
+        <v>30.294256086</v>
       </c>
       <c r="R23">
-        <v>0.2658227848101266</v>
+        <v>0.282051282051282</v>
       </c>
       <c r="S23">
-        <v>0.1294218279745024</v>
+        <v>0.1304162097837327</v>
       </c>
       <c r="T23">
-        <v>1.216799487127507</v>
+        <v>1.231268954069192</v>
       </c>
       <c r="U23">
         <v>0.0503</v>
@@ -3211,7 +3211,7 @@
         </is>
       </c>
       <c r="Y23">
-        <v>14.8849045573154</v>
+        <v>14.20831798652833</v>
       </c>
       <c r="Z23">
         <v>0</v>
@@ -3219,22 +3219,22 @@
     </row>
     <row r="24">
       <c r="A24">
-        <v>0.22</v>
+        <v>0.23</v>
       </c>
       <c r="B24">
-        <v>0.1117947036313115</v>
+        <v>0.1117338331627661</v>
       </c>
       <c r="C24">
-        <v>148.8725366719939</v>
+        <v>147.1532796771168</v>
       </c>
       <c r="D24">
-        <v>164.3905366719939</v>
+        <v>164.4902796771168</v>
       </c>
       <c r="E24">
-        <v>8.317999999999994</v>
+        <v>10.137</v>
       </c>
       <c r="F24">
-        <v>40.01799999999999</v>
+        <v>41.837</v>
       </c>
       <c r="G24">
         <v>24.5</v>
@@ -3255,28 +3255,28 @@
         <v>28.6</v>
       </c>
       <c r="M24">
-        <v>2.0129054</v>
+        <v>2.1044011</v>
       </c>
       <c r="N24">
-        <v>26.5870946</v>
+        <v>26.4955989</v>
       </c>
       <c r="O24">
-        <v>2.392838514</v>
+        <v>2.384603901</v>
       </c>
       <c r="P24">
-        <v>24.194256086</v>
+        <v>24.110994999</v>
       </c>
       <c r="Q24">
-        <v>30.294256086</v>
+        <v>30.210994999</v>
       </c>
       <c r="R24">
-        <v>0.282051282051282</v>
+        <v>0.2987012987012987</v>
       </c>
       <c r="S24">
-        <v>0.1304162097837327</v>
+        <v>0.131436419691904</v>
       </c>
       <c r="T24">
-        <v>1.231268954069192</v>
+        <v>1.246114251321051</v>
       </c>
       <c r="U24">
         <v>0.0503</v>
@@ -3293,7 +3293,7 @@
         </is>
       </c>
       <c r="Y24">
-        <v>14.20831798652833</v>
+        <v>13.59056503059232</v>
       </c>
       <c r="Z24">
         <v>0</v>
@@ -3301,22 +3301,22 @@
     </row>
     <row r="25">
       <c r="A25">
-        <v>0.23</v>
+        <v>0.24</v>
       </c>
       <c r="B25">
-        <v>0.1117338331627661</v>
+        <v>0.1116729626942207</v>
       </c>
       <c r="C25">
-        <v>147.1532796771168</v>
+        <v>145.4341437927029</v>
       </c>
       <c r="D25">
-        <v>164.4902796771168</v>
+        <v>164.5901437927029</v>
       </c>
       <c r="E25">
-        <v>10.137</v>
+        <v>11.956</v>
       </c>
       <c r="F25">
-        <v>41.837</v>
+        <v>43.656</v>
       </c>
       <c r="G25">
         <v>24.5</v>
@@ -3337,28 +3337,28 @@
         <v>28.6</v>
       </c>
       <c r="M25">
-        <v>2.1044011</v>
+        <v>2.1958968</v>
       </c>
       <c r="N25">
-        <v>26.4955989</v>
+        <v>26.4041032</v>
       </c>
       <c r="O25">
-        <v>2.384603901</v>
+        <v>2.376369288</v>
       </c>
       <c r="P25">
-        <v>24.110994999</v>
+        <v>24.027733912</v>
       </c>
       <c r="Q25">
-        <v>30.210994999</v>
+        <v>30.127733912</v>
       </c>
       <c r="R25">
-        <v>0.2987012987012987</v>
+        <v>0.3157894736842106</v>
       </c>
       <c r="S25">
-        <v>0.131436419691904</v>
+        <v>0.1324834772292378</v>
       </c>
       <c r="T25">
-        <v>1.246114251321051</v>
+        <v>1.261350214290065</v>
       </c>
       <c r="U25">
         <v>0.0503</v>
@@ -3375,7 +3375,7 @@
         </is>
       </c>
       <c r="Y25">
-        <v>13.59056503059232</v>
+        <v>13.02429148765097</v>
       </c>
       <c r="Z25">
         <v>0</v>
@@ -3383,22 +3383,22 @@
     </row>
     <row r="26">
       <c r="A26">
-        <v>0.24</v>
+        <v>0.25</v>
       </c>
       <c r="B26">
-        <v>0.1116729626942207</v>
+        <v>0.1119533422256754</v>
       </c>
       <c r="C26">
-        <v>145.434143792703</v>
+        <v>143.1561572907621</v>
       </c>
       <c r="D26">
-        <v>164.590143792703</v>
+        <v>164.1311572907621</v>
       </c>
       <c r="E26">
-        <v>11.95599999999999</v>
+        <v>13.775</v>
       </c>
       <c r="F26">
-        <v>43.65599999999999</v>
+        <v>45.47499999999999</v>
       </c>
       <c r="G26">
         <v>24.5</v>
@@ -3419,45 +3419,45 @@
         <v>28.6</v>
       </c>
       <c r="M26">
-        <v>2.195896799999999</v>
+        <v>2.355605</v>
       </c>
       <c r="N26">
-        <v>26.4041032</v>
+        <v>26.244395</v>
       </c>
       <c r="O26">
-        <v>2.376369288</v>
+        <v>2.36199555</v>
       </c>
       <c r="P26">
-        <v>24.027733912</v>
+        <v>23.88239945</v>
       </c>
       <c r="Q26">
-        <v>30.127733912</v>
+        <v>29.98239945</v>
       </c>
       <c r="R26">
-        <v>0.3157894736842105</v>
+        <v>0.3333333333333333</v>
       </c>
       <c r="S26">
-        <v>0.1324834772292378</v>
+        <v>0.1335584563009005</v>
       </c>
       <c r="T26">
-        <v>1.261350214290065</v>
+        <v>1.276992469604918</v>
       </c>
       <c r="U26">
-        <v>0.0503</v>
+        <v>0.0518</v>
       </c>
       <c r="V26">
         <v>0.09</v>
       </c>
       <c r="W26">
-        <v>0.045773</v>
+        <v>0.047138</v>
       </c>
       <c r="X26" t="inlineStr">
         <is>
-          <t>Aaa/AAA</t>
+          <t>Aa2/AA</t>
         </is>
       </c>
       <c r="Y26">
-        <v>13.02429148765097</v>
+        <v>12.14125458215618</v>
       </c>
       <c r="Z26">
         <v>0</v>
@@ -3465,22 +3465,22 @@
     </row>
     <row r="27">
       <c r="A27">
-        <v>0.25</v>
+        <v>0.26</v>
       </c>
       <c r="B27">
-        <v>0.1119533422256754</v>
+        <v>0.11190612175713</v>
       </c>
       <c r="C27">
-        <v>143.1561572907621</v>
+        <v>141.4142787297418</v>
       </c>
       <c r="D27">
-        <v>164.1311572907621</v>
+        <v>164.2082787297418</v>
       </c>
       <c r="E27">
-        <v>13.775</v>
+        <v>15.594</v>
       </c>
       <c r="F27">
-        <v>45.47499999999999</v>
+        <v>47.294</v>
       </c>
       <c r="G27">
         <v>24.5</v>
@@ -3501,28 +3501,28 @@
         <v>28.6</v>
       </c>
       <c r="M27">
-        <v>2.355605</v>
+        <v>2.4498292</v>
       </c>
       <c r="N27">
-        <v>26.244395</v>
+        <v>26.1501708</v>
       </c>
       <c r="O27">
-        <v>2.36199555</v>
+        <v>2.353515372</v>
       </c>
       <c r="P27">
-        <v>23.88239945</v>
+        <v>23.796655428</v>
       </c>
       <c r="Q27">
-        <v>29.98239945</v>
+        <v>29.896655428</v>
       </c>
       <c r="R27">
-        <v>0.3333333333333333</v>
+        <v>0.3513513513513514</v>
       </c>
       <c r="S27">
-        <v>0.1335584563009005</v>
+        <v>0.1346624888609864</v>
       </c>
       <c r="T27">
-        <v>1.276992469604918</v>
+        <v>1.29305748857693</v>
       </c>
       <c r="U27">
         <v>0.0518</v>
@@ -3539,7 +3539,7 @@
         </is>
       </c>
       <c r="Y27">
-        <v>12.14125458215618</v>
+        <v>11.67428325207325</v>
       </c>
       <c r="Z27">
         <v>0</v>
@@ -3547,22 +3547,22 @@
     </row>
     <row r="28">
       <c r="A28">
-        <v>0.26</v>
+        <v>0.27</v>
       </c>
       <c r="B28">
-        <v>0.11190612175713</v>
+        <v>0.1118589012885846</v>
       </c>
       <c r="C28">
-        <v>141.4142787297418</v>
+        <v>139.6724726779569</v>
       </c>
       <c r="D28">
-        <v>164.2082787297418</v>
+        <v>164.2854726779569</v>
       </c>
       <c r="E28">
-        <v>15.594</v>
+        <v>17.413</v>
       </c>
       <c r="F28">
-        <v>47.294</v>
+        <v>49.113</v>
       </c>
       <c r="G28">
         <v>24.5</v>
@@ -3583,28 +3583,28 @@
         <v>28.6</v>
       </c>
       <c r="M28">
-        <v>2.4498292</v>
+        <v>2.5440534</v>
       </c>
       <c r="N28">
-        <v>26.1501708</v>
+        <v>26.0559466</v>
       </c>
       <c r="O28">
-        <v>2.353515372</v>
+        <v>2.345035194</v>
       </c>
       <c r="P28">
-        <v>23.796655428</v>
+        <v>23.710911406</v>
       </c>
       <c r="Q28">
-        <v>29.896655428</v>
+        <v>29.810911406</v>
       </c>
       <c r="R28">
-        <v>0.3513513513513514</v>
+        <v>0.3698630136986302</v>
       </c>
       <c r="S28">
-        <v>0.1346624888609864</v>
+        <v>0.135796768888472</v>
       </c>
       <c r="T28">
-        <v>1.29305748857693</v>
+        <v>1.309562645055024</v>
       </c>
       <c r="U28">
         <v>0.0518</v>
@@ -3621,7 +3621,7 @@
         </is>
       </c>
       <c r="Y28">
-        <v>11.67428325207325</v>
+        <v>11.24190239088535</v>
       </c>
       <c r="Z28">
         <v>0</v>
@@ -3629,22 +3629,22 @@
     </row>
     <row r="29">
       <c r="A29">
-        <v>0.27</v>
+        <v>0.28</v>
       </c>
       <c r="B29">
-        <v>0.1118589012885846</v>
+        <v>0.1118116808200392</v>
       </c>
       <c r="C29">
-        <v>139.6724726779569</v>
+        <v>137.9307392377147</v>
       </c>
       <c r="D29">
-        <v>164.2854726779569</v>
+        <v>164.3627392377147</v>
       </c>
       <c r="E29">
-        <v>17.413</v>
+        <v>19.232</v>
       </c>
       <c r="F29">
-        <v>49.113</v>
+        <v>50.932</v>
       </c>
       <c r="G29">
         <v>24.5</v>
@@ -3665,28 +3665,28 @@
         <v>28.6</v>
       </c>
       <c r="M29">
-        <v>2.5440534</v>
+        <v>2.6382776</v>
       </c>
       <c r="N29">
-        <v>26.0559466</v>
+        <v>25.9617224</v>
       </c>
       <c r="O29">
-        <v>2.345035194</v>
+        <v>2.336555016</v>
       </c>
       <c r="P29">
-        <v>23.710911406</v>
+        <v>23.625167384</v>
       </c>
       <c r="Q29">
-        <v>29.810911406</v>
+        <v>29.725167384</v>
       </c>
       <c r="R29">
-        <v>0.3698630136986302</v>
+        <v>0.388888888888889</v>
       </c>
       <c r="S29">
-        <v>0.135796768888472</v>
+        <v>0.1369625566944989</v>
       </c>
       <c r="T29">
-        <v>1.309562645055024</v>
+        <v>1.326526278101955</v>
       </c>
       <c r="U29">
         <v>0.0518</v>
@@ -3703,7 +3703,7 @@
         </is>
       </c>
       <c r="Y29">
-        <v>11.24190239088535</v>
+        <v>10.84040587692516</v>
       </c>
       <c r="Z29">
         <v>0</v>
@@ -3711,22 +3711,22 @@
     </row>
     <row r="30">
       <c r="A30">
-        <v>0.28</v>
+        <v>0.29</v>
       </c>
       <c r="B30">
-        <v>0.1118116808200392</v>
+        <v>0.1117644603514938</v>
       </c>
       <c r="C30">
-        <v>137.9307392377147</v>
+        <v>136.1890785115152</v>
       </c>
       <c r="D30">
-        <v>164.3627392377147</v>
+        <v>164.4400785115152</v>
       </c>
       <c r="E30">
-        <v>19.232</v>
+        <v>21.051</v>
       </c>
       <c r="F30">
-        <v>50.932</v>
+        <v>52.751</v>
       </c>
       <c r="G30">
         <v>24.5</v>
@@ -3747,28 +3747,28 @@
         <v>28.6</v>
       </c>
       <c r="M30">
-        <v>2.6382776</v>
+        <v>2.7325018</v>
       </c>
       <c r="N30">
-        <v>25.9617224</v>
+        <v>25.8674982</v>
       </c>
       <c r="O30">
-        <v>2.336555016</v>
+        <v>2.328074838</v>
       </c>
       <c r="P30">
-        <v>23.625167384</v>
+        <v>23.539423362</v>
       </c>
       <c r="Q30">
-        <v>29.725167384</v>
+        <v>29.639423362</v>
       </c>
       <c r="R30">
-        <v>0.388888888888889</v>
+        <v>0.4084507042253522</v>
       </c>
       <c r="S30">
-        <v>0.1369625566944989</v>
+        <v>0.1381611835936533</v>
       </c>
       <c r="T30">
-        <v>1.326526278101955</v>
+        <v>1.343967759967108</v>
       </c>
       <c r="U30">
         <v>0.0518</v>
@@ -3785,7 +3785,7 @@
         </is>
       </c>
       <c r="Y30">
-        <v>10.84040587692516</v>
+        <v>10.46659877772084</v>
       </c>
       <c r="Z30">
         <v>0</v>
@@ -3793,22 +3793,22 @@
     </row>
     <row r="31">
       <c r="A31">
-        <v>0.29</v>
+        <v>0.3</v>
       </c>
       <c r="B31">
-        <v>0.1117644603514938</v>
+        <v>0.1117172398829484</v>
       </c>
       <c r="C31">
-        <v>136.1890785115152</v>
+        <v>134.4474906020514</v>
       </c>
       <c r="D31">
-        <v>164.4400785115152</v>
+        <v>164.5174906020514</v>
       </c>
       <c r="E31">
-        <v>21.05099999999999</v>
+        <v>22.86999999999999</v>
       </c>
       <c r="F31">
-        <v>52.75099999999999</v>
+        <v>54.56999999999999</v>
       </c>
       <c r="G31">
         <v>24.5</v>
@@ -3829,28 +3829,28 @@
         <v>28.6</v>
       </c>
       <c r="M31">
-        <v>2.7325018</v>
+        <v>2.826725999999999</v>
       </c>
       <c r="N31">
-        <v>25.8674982</v>
+        <v>25.773274</v>
       </c>
       <c r="O31">
-        <v>2.328074838</v>
+        <v>2.31959466</v>
       </c>
       <c r="P31">
-        <v>23.539423362</v>
+        <v>23.45367934</v>
       </c>
       <c r="Q31">
-        <v>29.639423362</v>
+        <v>29.55367934</v>
       </c>
       <c r="R31">
-        <v>0.4084507042253521</v>
+        <v>0.4285714285714286</v>
       </c>
       <c r="S31">
-        <v>0.1381611835936533</v>
+        <v>0.1393940569756406</v>
       </c>
       <c r="T31">
-        <v>1.343967759967108</v>
+        <v>1.361907569885552</v>
       </c>
       <c r="U31">
         <v>0.0518</v>
@@ -3867,7 +3867,7 @@
         </is>
       </c>
       <c r="Y31">
-        <v>10.46659877772084</v>
+        <v>10.11771215179682</v>
       </c>
       <c r="Z31">
         <v>0</v>
@@ -3875,22 +3875,22 @@
     </row>
     <row r="32">
       <c r="A32">
-        <v>0.3</v>
+        <v>0.31</v>
       </c>
       <c r="B32">
-        <v>0.1117172398829484</v>
+        <v>0.1121495894144031</v>
       </c>
       <c r="C32">
-        <v>134.4474906020514</v>
+        <v>131.9224169785849</v>
       </c>
       <c r="D32">
-        <v>164.5174906020514</v>
+        <v>163.8114169785849</v>
       </c>
       <c r="E32">
-        <v>22.86999999999999</v>
+        <v>24.689</v>
       </c>
       <c r="F32">
-        <v>54.56999999999999</v>
+        <v>56.389</v>
       </c>
       <c r="G32">
         <v>24.5</v>
@@ -3911,45 +3911,45 @@
         <v>28.6</v>
       </c>
       <c r="M32">
-        <v>2.826725999999999</v>
+        <v>3.0168115</v>
       </c>
       <c r="N32">
-        <v>25.773274</v>
+        <v>25.5831885</v>
       </c>
       <c r="O32">
-        <v>2.31959466</v>
+        <v>2.302486965</v>
       </c>
       <c r="P32">
-        <v>23.45367934</v>
+        <v>23.280701535</v>
       </c>
       <c r="Q32">
-        <v>29.55367934</v>
+        <v>29.380701535</v>
       </c>
       <c r="R32">
-        <v>0.4285714285714286</v>
+        <v>0.4492753623188406</v>
       </c>
       <c r="S32">
-        <v>0.1393940569756406</v>
+        <v>0.1406626658179755</v>
       </c>
       <c r="T32">
-        <v>1.361907569885552</v>
+        <v>1.380367374294386</v>
       </c>
       <c r="U32">
-        <v>0.0518</v>
+        <v>0.0535</v>
       </c>
       <c r="V32">
         <v>0.09</v>
       </c>
       <c r="W32">
-        <v>0.047138</v>
+        <v>0.048685</v>
       </c>
       <c r="X32" t="inlineStr">
         <is>
-          <t>Aa2/AA</t>
+          <t>A1/A+</t>
         </is>
       </c>
       <c r="Y32">
-        <v>10.11771215179682</v>
+        <v>9.48020782869596</v>
       </c>
       <c r="Z32">
         <v>0</v>
@@ -3957,22 +3957,22 @@
     </row>
     <row r="33">
       <c r="A33">
-        <v>0.31</v>
+        <v>0.32</v>
       </c>
       <c r="B33">
-        <v>0.1121495894144031</v>
+        <v>0.1121178389458577</v>
       </c>
       <c r="C33">
-        <v>131.9224169785849</v>
+        <v>130.1550626734698</v>
       </c>
       <c r="D33">
-        <v>163.8114169785849</v>
+        <v>163.8630626734698</v>
       </c>
       <c r="E33">
-        <v>24.689</v>
+        <v>26.50799999999999</v>
       </c>
       <c r="F33">
-        <v>56.389</v>
+        <v>58.20799999999999</v>
       </c>
       <c r="G33">
         <v>24.5</v>
@@ -3993,28 +3993,28 @@
         <v>28.6</v>
       </c>
       <c r="M33">
-        <v>3.0168115</v>
+        <v>3.114128</v>
       </c>
       <c r="N33">
-        <v>25.5831885</v>
+        <v>25.485872</v>
       </c>
       <c r="O33">
-        <v>2.302486965</v>
+        <v>2.29372848</v>
       </c>
       <c r="P33">
-        <v>23.280701535</v>
+        <v>23.19214352</v>
       </c>
       <c r="Q33">
-        <v>29.380701535</v>
+        <v>29.29214352</v>
       </c>
       <c r="R33">
-        <v>0.4492753623188406</v>
+        <v>0.4705882352941177</v>
       </c>
       <c r="S33">
-        <v>0.1406626658179755</v>
+        <v>0.1419685866850848</v>
       </c>
       <c r="T33">
-        <v>1.380367374294386</v>
+        <v>1.399370114127008</v>
       </c>
       <c r="U33">
         <v>0.0535</v>
@@ -4031,7 +4031,7 @@
         </is>
       </c>
       <c r="Y33">
-        <v>9.48020782869596</v>
+        <v>9.183951334049212</v>
       </c>
       <c r="Z33">
         <v>0</v>
@@ -4039,22 +4039,22 @@
     </row>
     <row r="34">
       <c r="A34">
-        <v>0.32</v>
+        <v>0.33</v>
       </c>
       <c r="B34">
-        <v>0.1121178389458577</v>
+        <v>0.1120860884773123</v>
       </c>
       <c r="C34">
-        <v>130.1550626734698</v>
+        <v>128.3877409438495</v>
       </c>
       <c r="D34">
-        <v>163.8630626734698</v>
+        <v>163.9147409438495</v>
       </c>
       <c r="E34">
-        <v>26.50799999999999</v>
+        <v>28.32699999999999</v>
       </c>
       <c r="F34">
-        <v>58.20799999999999</v>
+        <v>60.02699999999999</v>
       </c>
       <c r="G34">
         <v>24.5</v>
@@ -4075,28 +4075,28 @@
         <v>28.6</v>
       </c>
       <c r="M34">
-        <v>3.114128</v>
+        <v>3.2114445</v>
       </c>
       <c r="N34">
-        <v>25.485872</v>
+        <v>25.3885555</v>
       </c>
       <c r="O34">
-        <v>2.29372848</v>
+        <v>2.284969995</v>
       </c>
       <c r="P34">
-        <v>23.19214352</v>
+        <v>23.103585505</v>
       </c>
       <c r="Q34">
-        <v>29.29214352</v>
+        <v>29.203585505</v>
       </c>
       <c r="R34">
-        <v>0.4705882352941177</v>
+        <v>0.4925373134328359</v>
       </c>
       <c r="S34">
-        <v>0.1419685866850848</v>
+        <v>0.1433134902646452</v>
       </c>
       <c r="T34">
-        <v>1.399370114127008</v>
+        <v>1.418940099924784</v>
       </c>
       <c r="U34">
         <v>0.0535</v>
@@ -4113,7 +4113,7 @@
         </is>
       </c>
       <c r="Y34">
-        <v>9.183951334049212</v>
+        <v>8.905649778471963</v>
       </c>
       <c r="Z34">
         <v>0</v>
@@ -4121,22 +4121,22 @@
     </row>
     <row r="35">
       <c r="A35">
-        <v>0.33</v>
+        <v>0.34</v>
       </c>
       <c r="B35">
-        <v>0.1120860884773123</v>
+        <v>0.1120543380087669</v>
       </c>
       <c r="C35">
-        <v>128.3877409438495</v>
+        <v>126.6204518205544</v>
       </c>
       <c r="D35">
-        <v>163.9147409438495</v>
+        <v>163.9664518205544</v>
       </c>
       <c r="E35">
-        <v>28.32699999999999</v>
+        <v>30.146</v>
       </c>
       <c r="F35">
-        <v>60.02699999999999</v>
+        <v>61.846</v>
       </c>
       <c r="G35">
         <v>24.5</v>
@@ -4157,28 +4157,28 @@
         <v>28.6</v>
       </c>
       <c r="M35">
-        <v>3.2114445</v>
+        <v>3.308761</v>
       </c>
       <c r="N35">
-        <v>25.3885555</v>
+        <v>25.291239</v>
       </c>
       <c r="O35">
-        <v>2.284969995</v>
+        <v>2.27621151</v>
       </c>
       <c r="P35">
-        <v>23.103585505</v>
+        <v>23.01502749</v>
       </c>
       <c r="Q35">
-        <v>29.203585505</v>
+        <v>29.11502749</v>
       </c>
       <c r="R35">
-        <v>0.4925373134328359</v>
+        <v>0.5151515151515152</v>
       </c>
       <c r="S35">
-        <v>0.1433134902646452</v>
+        <v>0.1446991484981317</v>
       </c>
       <c r="T35">
-        <v>1.418940099924784</v>
+        <v>1.43910311559522</v>
       </c>
       <c r="U35">
         <v>0.0535</v>
@@ -4195,7 +4195,7 @@
         </is>
       </c>
       <c r="Y35">
-        <v>8.905649778471963</v>
+        <v>8.643718902634554</v>
       </c>
       <c r="Z35">
         <v>0</v>
@@ -4203,22 +4203,22 @@
     </row>
     <row r="36">
       <c r="A36">
-        <v>0.34</v>
+        <v>0.35</v>
       </c>
       <c r="B36">
-        <v>0.1120543380087669</v>
+        <v>0.1120225875402216</v>
       </c>
       <c r="C36">
-        <v>126.6204518205544</v>
+        <v>124.8531953344535</v>
       </c>
       <c r="D36">
-        <v>163.9664518205544</v>
+        <v>164.0181953344535</v>
       </c>
       <c r="E36">
-        <v>30.146</v>
+        <v>31.965</v>
       </c>
       <c r="F36">
-        <v>61.846</v>
+        <v>63.665</v>
       </c>
       <c r="G36">
         <v>24.5</v>
@@ -4239,28 +4239,28 @@
         <v>28.6</v>
       </c>
       <c r="M36">
-        <v>3.308761</v>
+        <v>3.4060775</v>
       </c>
       <c r="N36">
-        <v>25.291239</v>
+        <v>25.1939225</v>
       </c>
       <c r="O36">
-        <v>2.27621151</v>
+        <v>2.267453025</v>
       </c>
       <c r="P36">
-        <v>23.01502749</v>
+        <v>22.926469475</v>
       </c>
       <c r="Q36">
-        <v>29.11502749</v>
+        <v>29.02646947500001</v>
       </c>
       <c r="R36">
-        <v>0.5151515151515152</v>
+        <v>0.5384615384615385</v>
       </c>
       <c r="S36">
-        <v>0.1446991484981317</v>
+        <v>0.1461274423695716</v>
       </c>
       <c r="T36">
-        <v>1.43910311559522</v>
+        <v>1.459886531747822</v>
       </c>
       <c r="U36">
         <v>0.0535</v>
@@ -4277,7 +4277,7 @@
         </is>
       </c>
       <c r="Y36">
-        <v>8.643718902634554</v>
+        <v>8.396755505416422</v>
       </c>
       <c r="Z36">
         <v>0</v>
@@ -4285,22 +4285,22 @@
     </row>
     <row r="37">
       <c r="A37">
-        <v>0.35</v>
+        <v>0.36</v>
       </c>
       <c r="B37">
-        <v>0.1120225875402216</v>
+        <v>0.1119908370716762</v>
       </c>
       <c r="C37">
-        <v>124.8531953344535</v>
+        <v>123.085971516455</v>
       </c>
       <c r="D37">
-        <v>164.0181953344535</v>
+        <v>164.069971516455</v>
       </c>
       <c r="E37">
-        <v>31.965</v>
+        <v>33.78399999999999</v>
       </c>
       <c r="F37">
-        <v>63.665</v>
+        <v>65.48399999999999</v>
       </c>
       <c r="G37">
         <v>24.5</v>
@@ -4321,28 +4321,28 @@
         <v>28.6</v>
       </c>
       <c r="M37">
-        <v>3.4060775</v>
+        <v>3.503394</v>
       </c>
       <c r="N37">
-        <v>25.1939225</v>
+        <v>25.096606</v>
       </c>
       <c r="O37">
-        <v>2.267453025</v>
+        <v>2.25869454</v>
       </c>
       <c r="P37">
-        <v>22.926469475</v>
+        <v>22.83791146</v>
       </c>
       <c r="Q37">
-        <v>29.02646947500001</v>
+        <v>28.93791146</v>
       </c>
       <c r="R37">
-        <v>0.5384615384615385</v>
+        <v>0.5625000000000001</v>
       </c>
       <c r="S37">
-        <v>0.1461274423695716</v>
+        <v>0.147600370424494</v>
       </c>
       <c r="T37">
-        <v>1.459886531747822</v>
+        <v>1.481319429655194</v>
       </c>
       <c r="U37">
         <v>0.0535</v>
@@ -4359,7 +4359,7 @@
         </is>
       </c>
       <c r="Y37">
-        <v>8.396755505416422</v>
+        <v>8.163512296932634</v>
       </c>
       <c r="Z37">
         <v>0</v>
@@ -4367,22 +4367,22 @@
     </row>
     <row r="38">
       <c r="A38">
-        <v>0.36</v>
+        <v>0.37</v>
       </c>
       <c r="B38">
-        <v>0.1119908370716762</v>
+        <v>0.1119590866031308</v>
       </c>
       <c r="C38">
-        <v>123.085971516455</v>
+        <v>121.3187803975058</v>
       </c>
       <c r="D38">
-        <v>164.069971516455</v>
+        <v>164.1217803975058</v>
       </c>
       <c r="E38">
-        <v>33.78399999999999</v>
+        <v>35.60299999999999</v>
       </c>
       <c r="F38">
-        <v>65.48399999999999</v>
+        <v>67.303</v>
       </c>
       <c r="G38">
         <v>24.5</v>
@@ -4403,28 +4403,28 @@
         <v>28.6</v>
       </c>
       <c r="M38">
-        <v>3.503394</v>
+        <v>3.6007105</v>
       </c>
       <c r="N38">
-        <v>25.096606</v>
+        <v>24.9992895</v>
       </c>
       <c r="O38">
-        <v>2.25869454</v>
+        <v>2.249936055</v>
       </c>
       <c r="P38">
-        <v>22.83791146</v>
+        <v>22.749353445</v>
       </c>
       <c r="Q38">
-        <v>28.93791146</v>
+        <v>28.84935344500001</v>
       </c>
       <c r="R38">
-        <v>0.5625</v>
+        <v>0.5873015873015873</v>
       </c>
       <c r="S38">
-        <v>0.147600370424494</v>
+        <v>0.1491200581002076</v>
       </c>
       <c r="T38">
-        <v>1.481319429655193</v>
+        <v>1.503432737019942</v>
       </c>
       <c r="U38">
         <v>0.0535</v>
@@ -4441,7 +4441,7 @@
         </is>
       </c>
       <c r="Y38">
-        <v>8.163512296932634</v>
+        <v>7.942876829447967</v>
       </c>
       <c r="Z38">
         <v>0</v>
@@ -4449,22 +4449,22 @@
     </row>
     <row r="39">
       <c r="A39">
-        <v>0.37</v>
+        <v>0.38</v>
       </c>
       <c r="B39">
-        <v>0.1119590866031308</v>
+        <v>0.1119273361345854</v>
       </c>
       <c r="C39">
-        <v>121.3187803975058</v>
+        <v>119.5516220085924</v>
       </c>
       <c r="D39">
-        <v>164.1217803975058</v>
+        <v>164.1736220085924</v>
       </c>
       <c r="E39">
-        <v>35.60299999999999</v>
+        <v>37.42199999999998</v>
       </c>
       <c r="F39">
-        <v>67.303</v>
+        <v>69.12199999999999</v>
       </c>
       <c r="G39">
         <v>24.5</v>
@@ -4485,28 +4485,28 @@
         <v>28.6</v>
       </c>
       <c r="M39">
-        <v>3.6007105</v>
+        <v>3.698026999999999</v>
       </c>
       <c r="N39">
-        <v>24.9992895</v>
+        <v>24.901973</v>
       </c>
       <c r="O39">
-        <v>2.249936055</v>
+        <v>2.24117757</v>
       </c>
       <c r="P39">
-        <v>22.749353445</v>
+        <v>22.66079543</v>
       </c>
       <c r="Q39">
-        <v>28.84935344500001</v>
+        <v>28.76079543</v>
       </c>
       <c r="R39">
-        <v>0.5873015873015873</v>
+        <v>0.6129032258064516</v>
       </c>
       <c r="S39">
-        <v>0.1491200581002076</v>
+        <v>0.1506887679590087</v>
       </c>
       <c r="T39">
-        <v>1.503432737019942</v>
+        <v>1.526259376880327</v>
       </c>
       <c r="U39">
         <v>0.0535</v>
@@ -4523,7 +4523,7 @@
         </is>
       </c>
       <c r="Y39">
-        <v>7.942876829447967</v>
+        <v>7.733853754988811</v>
       </c>
       <c r="Z39">
         <v>0</v>
@@ -4531,22 +4531,22 @@
     </row>
     <row r="40">
       <c r="A40">
-        <v>0.38</v>
+        <v>0.39</v>
       </c>
       <c r="B40">
-        <v>0.1119273361345854</v>
+        <v>0.11217950566604</v>
       </c>
       <c r="C40">
-        <v>119.5516220085924</v>
+        <v>117.3217846224372</v>
       </c>
       <c r="D40">
-        <v>164.1736220085924</v>
+        <v>163.7627846224372</v>
       </c>
       <c r="E40">
-        <v>37.42199999999998</v>
+        <v>39.24099999999999</v>
       </c>
       <c r="F40">
-        <v>69.12199999999999</v>
+        <v>70.94099999999999</v>
       </c>
       <c r="G40">
         <v>24.5</v>
@@ -4567,45 +4567,45 @@
         <v>28.6</v>
       </c>
       <c r="M40">
-        <v>3.698026999999999</v>
+        <v>3.852096299999999</v>
       </c>
       <c r="N40">
-        <v>24.901973</v>
+        <v>24.7479037</v>
       </c>
       <c r="O40">
-        <v>2.24117757</v>
+        <v>2.227311333</v>
       </c>
       <c r="P40">
-        <v>22.66079543</v>
+        <v>22.520592367</v>
       </c>
       <c r="Q40">
-        <v>28.76079543</v>
+        <v>28.620592367</v>
       </c>
       <c r="R40">
-        <v>0.6129032258064516</v>
+        <v>0.639344262295082</v>
       </c>
       <c r="S40">
-        <v>0.1506887679590087</v>
+        <v>0.1523089109279345</v>
       </c>
       <c r="T40">
-        <v>1.526259376880327</v>
+        <v>1.549834431162365</v>
       </c>
       <c r="U40">
-        <v>0.0535</v>
+        <v>0.0543</v>
       </c>
       <c r="V40">
         <v>0.09</v>
       </c>
       <c r="W40">
-        <v>0.048685</v>
+        <v>0.04941300000000001</v>
       </c>
       <c r="X40" t="inlineStr">
         <is>
-          <t>A1/A+</t>
+          <t>A2/A</t>
         </is>
       </c>
       <c r="Y40">
-        <v>7.733853754988811</v>
+        <v>7.424528820839709</v>
       </c>
       <c r="Z40">
         <v>0</v>
@@ -4613,22 +4613,22 @@
     </row>
     <row r="41">
       <c r="A41">
-        <v>0.39</v>
+        <v>0.4</v>
       </c>
       <c r="B41">
-        <v>0.11217950566604</v>
+        <v>0.1121550351974947</v>
       </c>
       <c r="C41">
-        <v>117.3217846224372</v>
+        <v>115.5425620727259</v>
       </c>
       <c r="D41">
-        <v>163.7627846224372</v>
+        <v>163.8025620727259</v>
       </c>
       <c r="E41">
-        <v>39.24099999999999</v>
+        <v>41.05999999999999</v>
       </c>
       <c r="F41">
-        <v>70.94099999999999</v>
+        <v>72.75999999999999</v>
       </c>
       <c r="G41">
         <v>24.5</v>
@@ -4649,28 +4649,28 @@
         <v>28.6</v>
       </c>
       <c r="M41">
-        <v>3.852096299999999</v>
+        <v>3.950867999999999</v>
       </c>
       <c r="N41">
-        <v>24.7479037</v>
+        <v>24.649132</v>
       </c>
       <c r="O41">
-        <v>2.227311333</v>
+        <v>2.21842188</v>
       </c>
       <c r="P41">
-        <v>22.520592367</v>
+        <v>22.43071012</v>
       </c>
       <c r="Q41">
-        <v>28.620592367</v>
+        <v>28.53071012</v>
       </c>
       <c r="R41">
-        <v>0.639344262295082</v>
+        <v>0.6666666666666667</v>
       </c>
       <c r="S41">
-        <v>0.1523089109279345</v>
+        <v>0.1539830586624911</v>
       </c>
       <c r="T41">
-        <v>1.549834431162365</v>
+        <v>1.574195320587137</v>
       </c>
       <c r="U41">
         <v>0.0543</v>
@@ -4687,7 +4687,7 @@
         </is>
       </c>
       <c r="Y41">
-        <v>7.424528820839709</v>
+        <v>7.238915600318716</v>
       </c>
       <c r="Z41">
         <v>0</v>
@@ -4695,22 +4695,22 @@
     </row>
     <row r="42">
       <c r="A42">
-        <v>0.4</v>
+        <v>0.41</v>
       </c>
       <c r="B42">
-        <v>0.1121550351974947</v>
+        <v>0.1121305647289493</v>
       </c>
       <c r="C42">
-        <v>115.5425620727259</v>
+        <v>113.7633588513373</v>
       </c>
       <c r="D42">
-        <v>163.8025620727259</v>
+        <v>163.8423588513373</v>
       </c>
       <c r="E42">
-        <v>41.05999999999999</v>
+        <v>42.87899999999999</v>
       </c>
       <c r="F42">
-        <v>72.75999999999999</v>
+        <v>74.57899999999999</v>
       </c>
       <c r="G42">
         <v>24.5</v>
@@ -4731,28 +4731,28 @@
         <v>28.6</v>
       </c>
       <c r="M42">
-        <v>3.950867999999999</v>
+        <v>4.049639699999999</v>
       </c>
       <c r="N42">
-        <v>24.649132</v>
+        <v>24.5503603</v>
       </c>
       <c r="O42">
-        <v>2.21842188</v>
+        <v>2.209532427</v>
       </c>
       <c r="P42">
-        <v>22.43071012</v>
+        <v>22.340827873</v>
       </c>
       <c r="Q42">
-        <v>28.53071012</v>
+        <v>28.440827873</v>
       </c>
       <c r="R42">
-        <v>0.6666666666666667</v>
+        <v>0.6949152542372882</v>
       </c>
       <c r="S42">
-        <v>0.1539830586624911</v>
+        <v>0.1557139571677107</v>
       </c>
       <c r="T42">
-        <v>1.574195320587137</v>
+        <v>1.599382002873766</v>
       </c>
       <c r="U42">
         <v>0.0543</v>
@@ -4769,7 +4769,7 @@
         </is>
       </c>
       <c r="Y42">
-        <v>7.238915600318716</v>
+        <v>7.062356683237772</v>
       </c>
       <c r="Z42">
         <v>0</v>
@@ -4777,22 +4777,22 @@
     </row>
     <row r="43">
       <c r="A43">
-        <v>0.41</v>
+        <v>0.42</v>
       </c>
       <c r="B43">
-        <v>0.1121305647289493</v>
+        <v>0.1121060942604039</v>
       </c>
       <c r="C43">
-        <v>113.7633588513373</v>
+        <v>111.9841749723624</v>
       </c>
       <c r="D43">
-        <v>163.8423588513373</v>
+        <v>163.8821749723624</v>
       </c>
       <c r="E43">
-        <v>42.87899999999999</v>
+        <v>44.69799999999999</v>
       </c>
       <c r="F43">
-        <v>74.57899999999999</v>
+        <v>76.398</v>
       </c>
       <c r="G43">
         <v>24.5</v>
@@ -4813,28 +4813,28 @@
         <v>28.6</v>
       </c>
       <c r="M43">
-        <v>4.049639699999999</v>
+        <v>4.1484114</v>
       </c>
       <c r="N43">
-        <v>24.5503603</v>
+        <v>24.4515886</v>
       </c>
       <c r="O43">
-        <v>2.209532427</v>
+        <v>2.200642974</v>
       </c>
       <c r="P43">
-        <v>22.340827873</v>
+        <v>22.250945626</v>
       </c>
       <c r="Q43">
-        <v>28.440827873</v>
+        <v>28.350945626</v>
       </c>
       <c r="R43">
-        <v>0.6949152542372882</v>
+        <v>0.7241379310344829</v>
       </c>
       <c r="S43">
-        <v>0.1557139571677107</v>
+        <v>0.1575045418282826</v>
       </c>
       <c r="T43">
-        <v>1.599382002873766</v>
+        <v>1.62543719144614</v>
       </c>
       <c r="U43">
         <v>0.0543</v>
@@ -4851,7 +4851,7 @@
         </is>
       </c>
       <c r="Y43">
-        <v>7.062356683237772</v>
+        <v>6.894205333636872</v>
       </c>
       <c r="Z43">
         <v>0</v>
@@ -4859,22 +4859,22 @@
     </row>
     <row r="44">
       <c r="A44">
-        <v>0.42</v>
+        <v>0.43</v>
       </c>
       <c r="B44">
-        <v>0.1121060942604039</v>
+        <v>0.1120816237918585</v>
       </c>
       <c r="C44">
-        <v>111.9841749723625</v>
+        <v>110.2050104499064</v>
       </c>
       <c r="D44">
-        <v>163.8821749723624</v>
+        <v>163.9220104499064</v>
       </c>
       <c r="E44">
-        <v>44.69799999999998</v>
+        <v>46.51699999999998</v>
       </c>
       <c r="F44">
-        <v>76.39799999999998</v>
+        <v>78.21699999999998</v>
       </c>
       <c r="G44">
         <v>24.5</v>
@@ -4895,28 +4895,28 @@
         <v>28.6</v>
       </c>
       <c r="M44">
-        <v>4.148411399999999</v>
+        <v>4.247183099999999</v>
       </c>
       <c r="N44">
-        <v>24.4515886</v>
+        <v>24.3528169</v>
       </c>
       <c r="O44">
-        <v>2.200642974</v>
+        <v>2.191753521</v>
       </c>
       <c r="P44">
-        <v>22.250945626</v>
+        <v>22.161063379</v>
       </c>
       <c r="Q44">
-        <v>28.350945626</v>
+        <v>28.261063379</v>
       </c>
       <c r="R44">
-        <v>0.7241379310344827</v>
+        <v>0.7543859649122806</v>
       </c>
       <c r="S44">
-        <v>0.1575045418282826</v>
+        <v>0.1593579540208044</v>
       </c>
       <c r="T44">
-        <v>1.62543719144614</v>
+        <v>1.652406597161405</v>
       </c>
       <c r="U44">
         <v>0.0543</v>
@@ -4933,7 +4933,7 @@
         </is>
       </c>
       <c r="Y44">
-        <v>6.894205333636873</v>
+        <v>6.733874977040666</v>
       </c>
       <c r="Z44">
         <v>0</v>
@@ -4941,22 +4941,22 @@
     </row>
     <row r="45">
       <c r="A45">
-        <v>0.43</v>
+        <v>0.44</v>
       </c>
       <c r="B45">
-        <v>0.1120816237918585</v>
+        <v>0.1120571533233132</v>
       </c>
       <c r="C45">
-        <v>110.2050104499064</v>
+        <v>108.4258652980876</v>
       </c>
       <c r="D45">
-        <v>163.9220104499064</v>
+        <v>163.9618652980876</v>
       </c>
       <c r="E45">
-        <v>46.51699999999998</v>
+        <v>48.33599999999998</v>
       </c>
       <c r="F45">
-        <v>78.21699999999998</v>
+        <v>80.03599999999999</v>
       </c>
       <c r="G45">
         <v>24.5</v>
@@ -4977,28 +4977,28 @@
         <v>28.6</v>
       </c>
       <c r="M45">
-        <v>4.247183099999999</v>
+        <v>4.345954799999999</v>
       </c>
       <c r="N45">
-        <v>24.3528169</v>
+        <v>24.2540452</v>
       </c>
       <c r="O45">
-        <v>2.191753521</v>
+        <v>2.182864068</v>
       </c>
       <c r="P45">
-        <v>22.161063379</v>
+        <v>22.071181132</v>
       </c>
       <c r="Q45">
-        <v>28.261063379</v>
+        <v>28.171181132</v>
       </c>
       <c r="R45">
-        <v>0.7543859649122806</v>
+        <v>0.7857142857142857</v>
       </c>
       <c r="S45">
-        <v>0.1593579540208044</v>
+        <v>0.1612775595059163</v>
       </c>
       <c r="T45">
-        <v>1.652406597161405</v>
+        <v>1.680339195937929</v>
       </c>
       <c r="U45">
         <v>0.0543</v>
@@ -5015,7 +5015,7 @@
         </is>
       </c>
       <c r="Y45">
-        <v>6.733874977040666</v>
+        <v>6.580832363926105</v>
       </c>
       <c r="Z45">
         <v>0</v>
@@ -5023,22 +5023,22 @@
     </row>
     <row r="46">
       <c r="A46">
-        <v>0.44</v>
+        <v>0.45</v>
       </c>
       <c r="B46">
-        <v>0.1120571533233132</v>
+        <v>0.1120326828547678</v>
       </c>
       <c r="C46">
-        <v>108.4258652980876</v>
+        <v>106.6467395310386</v>
       </c>
       <c r="D46">
-        <v>163.9618652980876</v>
+        <v>164.0017395310386</v>
       </c>
       <c r="E46">
-        <v>48.33599999999998</v>
+        <v>50.15499999999999</v>
       </c>
       <c r="F46">
-        <v>80.03599999999999</v>
+        <v>81.85499999999999</v>
       </c>
       <c r="G46">
         <v>24.5</v>
@@ -5059,28 +5059,28 @@
         <v>28.6</v>
       </c>
       <c r="M46">
-        <v>4.345954799999999</v>
+        <v>4.4447265</v>
       </c>
       <c r="N46">
-        <v>24.2540452</v>
+        <v>24.1552735</v>
       </c>
       <c r="O46">
-        <v>2.182864068</v>
+        <v>2.173974615</v>
       </c>
       <c r="P46">
-        <v>22.071181132</v>
+        <v>21.981298885</v>
       </c>
       <c r="Q46">
-        <v>28.171181132</v>
+        <v>28.081298885</v>
       </c>
       <c r="R46">
-        <v>0.7857142857142857</v>
+        <v>0.8181818181818181</v>
       </c>
       <c r="S46">
-        <v>0.1612775595059163</v>
+        <v>0.1632669688268505</v>
       </c>
       <c r="T46">
-        <v>1.680339195937929</v>
+        <v>1.709287525579055</v>
       </c>
       <c r="U46">
         <v>0.0543</v>
@@ -5097,7 +5097,7 @@
         </is>
       </c>
       <c r="Y46">
-        <v>6.580832363926105</v>
+        <v>6.434591644727747</v>
       </c>
       <c r="Z46">
         <v>0</v>
@@ -5105,22 +5105,22 @@
     </row>
     <row r="47">
       <c r="A47">
-        <v>0.45</v>
+        <v>0.46</v>
       </c>
       <c r="B47">
-        <v>0.1120326828547678</v>
+        <v>0.1120082123862224</v>
       </c>
       <c r="C47">
-        <v>106.6467395310386</v>
+        <v>104.8676331629054</v>
       </c>
       <c r="D47">
-        <v>164.0017395310386</v>
+        <v>164.0416331629054</v>
       </c>
       <c r="E47">
-        <v>50.15499999999999</v>
+        <v>51.97399999999999</v>
       </c>
       <c r="F47">
-        <v>81.85499999999999</v>
+        <v>83.67399999999999</v>
       </c>
       <c r="G47">
         <v>24.5</v>
@@ -5141,28 +5141,28 @@
         <v>28.6</v>
       </c>
       <c r="M47">
-        <v>4.4447265</v>
+        <v>4.543498199999999</v>
       </c>
       <c r="N47">
-        <v>24.1552735</v>
+        <v>24.0565018</v>
       </c>
       <c r="O47">
-        <v>2.173974615</v>
+        <v>2.165085162</v>
       </c>
       <c r="P47">
-        <v>21.981298885</v>
+        <v>21.891416638</v>
       </c>
       <c r="Q47">
-        <v>28.081298885</v>
+        <v>27.991416638</v>
       </c>
       <c r="R47">
-        <v>0.8181818181818181</v>
+        <v>0.8518518518518519</v>
       </c>
       <c r="S47">
-        <v>0.1632669688268505</v>
+        <v>0.1653300599744859</v>
       </c>
       <c r="T47">
-        <v>1.709287525579055</v>
+        <v>1.739308015577259</v>
       </c>
       <c r="U47">
         <v>0.0543</v>
@@ -5179,7 +5179,7 @@
         </is>
       </c>
       <c r="Y47">
-        <v>6.434591644727747</v>
+        <v>6.29470921766845</v>
       </c>
       <c r="Z47">
         <v>0</v>
@@ -5187,22 +5187,22 @@
     </row>
     <row r="48">
       <c r="A48">
-        <v>0.46</v>
+        <v>0.47</v>
       </c>
       <c r="B48">
-        <v>0.1120082123862224</v>
+        <v>0.111983741917677</v>
       </c>
       <c r="C48">
-        <v>104.8676331629054</v>
+        <v>103.088546207848</v>
       </c>
       <c r="D48">
-        <v>164.0416331629054</v>
+        <v>164.081546207848</v>
       </c>
       <c r="E48">
-        <v>51.97399999999999</v>
+        <v>53.79299999999999</v>
       </c>
       <c r="F48">
-        <v>83.67399999999999</v>
+        <v>85.49299999999999</v>
       </c>
       <c r="G48">
         <v>24.5</v>
@@ -5223,28 +5223,28 @@
         <v>28.6</v>
       </c>
       <c r="M48">
-        <v>4.543498199999999</v>
+        <v>4.6422699</v>
       </c>
       <c r="N48">
-        <v>24.0565018</v>
+        <v>23.9577301</v>
       </c>
       <c r="O48">
-        <v>2.165085162</v>
+        <v>2.156195709</v>
       </c>
       <c r="P48">
-        <v>21.891416638</v>
+        <v>21.801534391</v>
       </c>
       <c r="Q48">
-        <v>27.991416638</v>
+        <v>27.90153439100001</v>
       </c>
       <c r="R48">
-        <v>0.8518518518518519</v>
+        <v>0.8867924528301887</v>
       </c>
       <c r="S48">
-        <v>0.1653300599744859</v>
+        <v>0.1674710036182585</v>
       </c>
       <c r="T48">
-        <v>1.739308015577259</v>
+        <v>1.77046135425464</v>
       </c>
       <c r="U48">
         <v>0.0543</v>
@@ -5261,7 +5261,7 @@
         </is>
       </c>
       <c r="Y48">
-        <v>6.29470921766845</v>
+        <v>6.160779234313801</v>
       </c>
       <c r="Z48">
         <v>0</v>
@@ -5269,22 +5269,22 @@
     </row>
     <row r="49">
       <c r="A49">
-        <v>0.47</v>
+        <v>0.48</v>
       </c>
       <c r="B49">
-        <v>0.111983741917677</v>
+        <v>0.1123960714491316</v>
       </c>
       <c r="C49">
-        <v>103.088546207848</v>
+        <v>100.5995909644011</v>
       </c>
       <c r="D49">
-        <v>164.081546207848</v>
+        <v>163.4115909644011</v>
       </c>
       <c r="E49">
-        <v>53.79299999999999</v>
+        <v>55.61199999999999</v>
       </c>
       <c r="F49">
-        <v>85.49299999999999</v>
+        <v>87.312</v>
       </c>
       <c r="G49">
         <v>24.5</v>
@@ -5305,45 +5305,45 @@
         <v>28.6</v>
       </c>
       <c r="M49">
-        <v>4.6422699</v>
+        <v>4.8283536</v>
       </c>
       <c r="N49">
-        <v>23.9577301</v>
+        <v>23.7716464</v>
       </c>
       <c r="O49">
-        <v>2.156195709</v>
+        <v>2.139448176</v>
       </c>
       <c r="P49">
-        <v>21.801534391</v>
+        <v>21.632198224</v>
       </c>
       <c r="Q49">
-        <v>27.90153439100001</v>
+        <v>27.732198224</v>
       </c>
       <c r="R49">
-        <v>0.8867924528301887</v>
+        <v>0.9230769230769231</v>
       </c>
       <c r="S49">
-        <v>0.1674710036182585</v>
+        <v>0.1696942912483301</v>
       </c>
       <c r="T49">
-        <v>1.77046135425464</v>
+        <v>1.802812898265767</v>
       </c>
       <c r="U49">
-        <v>0.0543</v>
+        <v>0.0553</v>
       </c>
       <c r="V49">
         <v>0.09</v>
       </c>
       <c r="W49">
-        <v>0.04941300000000001</v>
+        <v>0.05032300000000001</v>
       </c>
       <c r="X49" t="inlineStr">
         <is>
-          <t>A2/A</t>
+          <t>A3/A-</t>
         </is>
       </c>
       <c r="Y49">
-        <v>6.160779234313801</v>
+        <v>5.9233441395013</v>
       </c>
       <c r="Z49">
         <v>0</v>
@@ -5351,22 +5351,22 @@
     </row>
     <row r="50">
       <c r="A50">
-        <v>0.48</v>
+        <v>0.49</v>
       </c>
       <c r="B50">
-        <v>0.1123960714491316</v>
+        <v>0.1123807009805863</v>
       </c>
       <c r="C50">
-        <v>100.5995909644012</v>
+        <v>98.80546680021116</v>
       </c>
       <c r="D50">
-        <v>163.4115909644012</v>
+        <v>163.4364668002112</v>
       </c>
       <c r="E50">
-        <v>55.61199999999998</v>
+        <v>57.43099999999998</v>
       </c>
       <c r="F50">
-        <v>87.31199999999998</v>
+        <v>89.13099999999999</v>
       </c>
       <c r="G50">
         <v>24.5</v>
@@ -5387,28 +5387,28 @@
         <v>28.6</v>
       </c>
       <c r="M50">
-        <v>4.828353599999999</v>
+        <v>4.9289443</v>
       </c>
       <c r="N50">
-        <v>23.7716464</v>
+        <v>23.6710557</v>
       </c>
       <c r="O50">
-        <v>2.139448176</v>
+        <v>2.130395013</v>
       </c>
       <c r="P50">
-        <v>21.632198224</v>
+        <v>21.540660687</v>
       </c>
       <c r="Q50">
-        <v>27.732198224</v>
+        <v>27.640660687</v>
       </c>
       <c r="R50">
-        <v>0.923076923076923</v>
+        <v>0.9607843137254901</v>
       </c>
       <c r="S50">
-        <v>0.16969429124833</v>
+        <v>0.1720047666286005</v>
       </c>
       <c r="T50">
-        <v>1.802812898265767</v>
+        <v>1.83643313027733</v>
       </c>
       <c r="U50">
         <v>0.0553</v>
@@ -5425,7 +5425,7 @@
         </is>
       </c>
       <c r="Y50">
-        <v>5.9233441395013</v>
+        <v>5.802459565225764</v>
       </c>
       <c r="Z50">
         <v>0</v>
@@ -5433,22 +5433,22 @@
     </row>
     <row r="51">
       <c r="A51">
-        <v>0.49</v>
+        <v>0.5</v>
       </c>
       <c r="B51">
-        <v>0.1123807009805863</v>
+        <v>0.1123653305120409</v>
       </c>
       <c r="C51">
-        <v>98.80546680021116</v>
+        <v>97.01135021077658</v>
       </c>
       <c r="D51">
-        <v>163.4364668002112</v>
+        <v>163.4613502107766</v>
       </c>
       <c r="E51">
-        <v>57.43099999999998</v>
+        <v>59.24999999999999</v>
       </c>
       <c r="F51">
-        <v>89.13099999999999</v>
+        <v>90.94999999999999</v>
       </c>
       <c r="G51">
         <v>24.5</v>
@@ -5469,28 +5469,28 @@
         <v>28.6</v>
       </c>
       <c r="M51">
-        <v>4.9289443</v>
+        <v>5.029534999999999</v>
       </c>
       <c r="N51">
-        <v>23.6710557</v>
+        <v>23.570465</v>
       </c>
       <c r="O51">
-        <v>2.130395013</v>
+        <v>2.12134185</v>
       </c>
       <c r="P51">
-        <v>21.540660687</v>
+        <v>21.44912315</v>
       </c>
       <c r="Q51">
-        <v>27.640660687</v>
+        <v>27.54912315</v>
       </c>
       <c r="R51">
-        <v>0.9607843137254901</v>
+        <v>1</v>
       </c>
       <c r="S51">
-        <v>0.1720047666286005</v>
+        <v>0.1744076610240818</v>
       </c>
       <c r="T51">
-        <v>1.83643313027733</v>
+        <v>1.871398171569356</v>
       </c>
       <c r="U51">
         <v>0.0553</v>
@@ -5507,7 +5507,7 @@
         </is>
       </c>
       <c r="Y51">
-        <v>5.802459565225764</v>
+        <v>5.686410373921248</v>
       </c>
       <c r="Z51">
         <v>0</v>
@@ -5515,22 +5515,22 @@
     </row>
     <row r="52">
       <c r="A52">
-        <v>0.5</v>
+        <v>0.51</v>
       </c>
       <c r="B52">
-        <v>0.1123653305120409</v>
+        <v>0.1123499600434955</v>
       </c>
       <c r="C52">
-        <v>97.01135021077658</v>
+        <v>95.21724119955785</v>
       </c>
       <c r="D52">
-        <v>163.4613502107766</v>
+        <v>163.4862411995578</v>
       </c>
       <c r="E52">
-        <v>59.24999999999999</v>
+        <v>61.06899999999999</v>
       </c>
       <c r="F52">
-        <v>90.94999999999999</v>
+        <v>92.76899999999999</v>
       </c>
       <c r="G52">
         <v>24.5</v>
@@ -5551,28 +5551,28 @@
         <v>28.6</v>
       </c>
       <c r="M52">
-        <v>5.029534999999999</v>
+        <v>5.1301257</v>
       </c>
       <c r="N52">
-        <v>23.570465</v>
+        <v>23.4698743</v>
       </c>
       <c r="O52">
-        <v>2.12134185</v>
+        <v>2.112288687</v>
       </c>
       <c r="P52">
-        <v>21.44912315</v>
+        <v>21.357585613</v>
       </c>
       <c r="Q52">
-        <v>27.54912315</v>
+        <v>27.457585613</v>
       </c>
       <c r="R52">
-        <v>1</v>
+        <v>1.040816326530612</v>
       </c>
       <c r="S52">
-        <v>0.1744076610240818</v>
+        <v>0.1769086327418276</v>
       </c>
       <c r="T52">
-        <v>1.871398171569356</v>
+        <v>1.907790357403913</v>
       </c>
       <c r="U52">
         <v>0.0553</v>
@@ -5589,7 +5589,7 @@
         </is>
       </c>
       <c r="Y52">
-        <v>5.686410373921248</v>
+        <v>5.574912131295341</v>
       </c>
       <c r="Z52">
         <v>0</v>
@@ -5597,22 +5597,22 @@
     </row>
     <row r="53">
       <c r="A53">
-        <v>0.51</v>
+        <v>0.52</v>
       </c>
       <c r="B53">
-        <v>0.1123499600434955</v>
+        <v>0.1123345895749501</v>
       </c>
       <c r="C53">
-        <v>95.21724119955785</v>
+        <v>93.42313977001734</v>
       </c>
       <c r="D53">
-        <v>163.4862411995578</v>
+        <v>163.5111397700173</v>
       </c>
       <c r="E53">
-        <v>61.06899999999999</v>
+        <v>62.88799999999999</v>
       </c>
       <c r="F53">
-        <v>92.76899999999999</v>
+        <v>94.58799999999999</v>
       </c>
       <c r="G53">
         <v>24.5</v>
@@ -5633,28 +5633,28 @@
         <v>28.6</v>
       </c>
       <c r="M53">
-        <v>5.1301257</v>
+        <v>5.230716399999999</v>
       </c>
       <c r="N53">
-        <v>23.4698743</v>
+        <v>23.3692836</v>
       </c>
       <c r="O53">
-        <v>2.112288687</v>
+        <v>2.103235524</v>
       </c>
       <c r="P53">
-        <v>21.357585613</v>
+        <v>21.266048076</v>
       </c>
       <c r="Q53">
-        <v>27.457585613</v>
+        <v>27.36604807600001</v>
       </c>
       <c r="R53">
-        <v>1.040816326530612</v>
+        <v>1.083333333333333</v>
       </c>
       <c r="S53">
-        <v>0.1769086327418276</v>
+        <v>0.1795138116144794</v>
       </c>
       <c r="T53">
-        <v>1.907790357403913</v>
+        <v>1.945698884314911</v>
       </c>
       <c r="U53">
         <v>0.0553</v>
@@ -5671,7 +5671,7 @@
         </is>
       </c>
       <c r="Y53">
-        <v>5.574912131295341</v>
+        <v>5.467702282616584</v>
       </c>
       <c r="Z53">
         <v>0</v>
@@ -5679,22 +5679,22 @@
     </row>
     <row r="54">
       <c r="A54">
-        <v>0.52</v>
+        <v>0.53</v>
       </c>
       <c r="B54">
-        <v>0.1123345895749501</v>
+        <v>0.1123192191064047</v>
       </c>
       <c r="C54">
-        <v>93.42313977001734</v>
+        <v>91.62904592561956</v>
       </c>
       <c r="D54">
-        <v>163.5111397700173</v>
+        <v>163.5360459256196</v>
       </c>
       <c r="E54">
-        <v>62.88799999999999</v>
+        <v>64.70699999999999</v>
       </c>
       <c r="F54">
-        <v>94.58799999999999</v>
+        <v>96.407</v>
       </c>
       <c r="G54">
         <v>24.5</v>
@@ -5715,28 +5715,28 @@
         <v>28.6</v>
       </c>
       <c r="M54">
-        <v>5.230716399999999</v>
+        <v>5.3313071</v>
       </c>
       <c r="N54">
-        <v>23.3692836</v>
+        <v>23.2686929</v>
       </c>
       <c r="O54">
-        <v>2.103235524</v>
+        <v>2.094182361</v>
       </c>
       <c r="P54">
-        <v>21.266048076</v>
+        <v>21.174510539</v>
       </c>
       <c r="Q54">
-        <v>27.36604807600001</v>
+        <v>27.274510539</v>
       </c>
       <c r="R54">
-        <v>1.083333333333333</v>
+        <v>1.127659574468085</v>
       </c>
       <c r="S54">
-        <v>0.1795138116144794</v>
+        <v>0.1822298491625633</v>
       </c>
       <c r="T54">
-        <v>1.945698884314911</v>
+        <v>1.985220540030631</v>
       </c>
       <c r="U54">
         <v>0.0553</v>
@@ -5753,7 +5753,7 @@
         </is>
       </c>
       <c r="Y54">
-        <v>5.467702282616584</v>
+        <v>5.364538088604951</v>
       </c>
       <c r="Z54">
         <v>0</v>
@@ -5761,22 +5761,22 @@
     </row>
     <row r="55">
       <c r="A55">
-        <v>0.53</v>
+        <v>0.54</v>
       </c>
       <c r="B55">
-        <v>0.1123192191064047</v>
+        <v>0.1123038486378594</v>
       </c>
       <c r="C55">
-        <v>91.62904592561956</v>
+        <v>89.83495966983125</v>
       </c>
       <c r="D55">
-        <v>163.5360459256196</v>
+        <v>163.5609596698312</v>
       </c>
       <c r="E55">
-        <v>64.70699999999999</v>
+        <v>66.526</v>
       </c>
       <c r="F55">
-        <v>96.407</v>
+        <v>98.226</v>
       </c>
       <c r="G55">
         <v>24.5</v>
@@ -5797,28 +5797,28 @@
         <v>28.6</v>
       </c>
       <c r="M55">
-        <v>5.3313071</v>
+        <v>5.4318978</v>
       </c>
       <c r="N55">
-        <v>23.2686929</v>
+        <v>23.1681022</v>
       </c>
       <c r="O55">
-        <v>2.094182361</v>
+        <v>2.085129198</v>
       </c>
       <c r="P55">
-        <v>21.174510539</v>
+        <v>21.082973002</v>
       </c>
       <c r="Q55">
-        <v>27.274510539</v>
+        <v>27.182973002</v>
       </c>
       <c r="R55">
-        <v>1.127659574468085</v>
+        <v>1.173913043478261</v>
       </c>
       <c r="S55">
-        <v>0.1822298491625633</v>
+        <v>0.1850639752996943</v>
       </c>
       <c r="T55">
-        <v>1.985220540030631</v>
+        <v>2.026460528603557</v>
       </c>
       <c r="U55">
         <v>0.0553</v>
@@ -5835,7 +5835,7 @@
         </is>
       </c>
       <c r="Y55">
-        <v>5.364538088604951</v>
+        <v>5.265194790667822</v>
       </c>
       <c r="Z55">
         <v>0</v>
@@ -5843,22 +5843,22 @@
     </row>
     <row r="56">
       <c r="A56">
-        <v>0.54</v>
+        <v>0.55</v>
       </c>
       <c r="B56">
-        <v>0.1123038486378594</v>
+        <v>0.112288478169314</v>
       </c>
       <c r="C56">
-        <v>89.83495966983125</v>
+        <v>88.04088100612113</v>
       </c>
       <c r="D56">
-        <v>163.5609596698312</v>
+        <v>163.5858810061211</v>
       </c>
       <c r="E56">
-        <v>66.526</v>
+        <v>68.345</v>
       </c>
       <c r="F56">
-        <v>98.226</v>
+        <v>100.045</v>
       </c>
       <c r="G56">
         <v>24.5</v>
@@ -5879,28 +5879,28 @@
         <v>28.6</v>
       </c>
       <c r="M56">
-        <v>5.4318978</v>
+        <v>5.5324885</v>
       </c>
       <c r="N56">
-        <v>23.1681022</v>
+        <v>23.0675115</v>
       </c>
       <c r="O56">
-        <v>2.085129198</v>
+        <v>2.076076035</v>
       </c>
       <c r="P56">
-        <v>21.082973002</v>
+        <v>20.991435465</v>
       </c>
       <c r="Q56">
-        <v>27.182973002</v>
+        <v>27.091435465</v>
       </c>
       <c r="R56">
-        <v>1.173913043478261</v>
+        <v>1.222222222222223</v>
       </c>
       <c r="S56">
-        <v>0.1850639752996943</v>
+        <v>0.1880240625984755</v>
       </c>
       <c r="T56">
-        <v>2.026460528603557</v>
+        <v>2.069533405557502</v>
       </c>
       <c r="U56">
         <v>0.0553</v>
@@ -5917,7 +5917,7 @@
         </is>
       </c>
       <c r="Y56">
-        <v>5.265194790667822</v>
+        <v>5.169463976292043</v>
       </c>
       <c r="Z56">
         <v>0</v>
@@ -5925,22 +5925,22 @@
     </row>
     <row r="57">
       <c r="A57">
-        <v>0.55</v>
+        <v>0.5600000000000001</v>
       </c>
       <c r="B57">
-        <v>0.112288478169314</v>
+        <v>0.1122731077007686</v>
       </c>
       <c r="C57">
-        <v>88.04088100612113</v>
+        <v>86.24680993796015</v>
       </c>
       <c r="D57">
-        <v>163.5858810061211</v>
+        <v>163.6108099379601</v>
       </c>
       <c r="E57">
-        <v>68.345</v>
+        <v>70.16399999999999</v>
       </c>
       <c r="F57">
-        <v>100.045</v>
+        <v>101.864</v>
       </c>
       <c r="G57">
         <v>24.5</v>
@@ -5961,28 +5961,28 @@
         <v>28.6</v>
       </c>
       <c r="M57">
-        <v>5.5324885</v>
+        <v>5.6330792</v>
       </c>
       <c r="N57">
-        <v>23.0675115</v>
+        <v>22.9669208</v>
       </c>
       <c r="O57">
-        <v>2.076076035</v>
+        <v>2.067022872</v>
       </c>
       <c r="P57">
-        <v>20.991435465</v>
+        <v>20.899897928</v>
       </c>
       <c r="Q57">
-        <v>27.091435465</v>
+        <v>26.999897928</v>
       </c>
       <c r="R57">
-        <v>1.222222222222223</v>
+        <v>1.272727272727273</v>
       </c>
       <c r="S57">
-        <v>0.1880240625984755</v>
+        <v>0.1911186993199286</v>
       </c>
       <c r="T57">
-        <v>2.069533405557502</v>
+        <v>2.114564140554807</v>
       </c>
       <c r="U57">
         <v>0.0553</v>
@@ -5999,7 +5999,7 @@
         </is>
       </c>
       <c r="Y57">
-        <v>5.169463976292043</v>
+        <v>5.077152119572542</v>
       </c>
       <c r="Z57">
         <v>0</v>
@@ -6007,22 +6007,22 @@
     </row>
     <row r="58">
       <c r="A58">
-        <v>0.5600000000000001</v>
+        <v>0.5700000000000001</v>
       </c>
       <c r="B58">
-        <v>0.1122731077007686</v>
+        <v>0.1122577372322232</v>
       </c>
       <c r="C58">
-        <v>86.24680993796015</v>
+        <v>84.45274646882112</v>
       </c>
       <c r="D58">
-        <v>163.6108099379601</v>
+        <v>163.6357464688211</v>
       </c>
       <c r="E58">
-        <v>70.16399999999999</v>
+        <v>71.98299999999999</v>
       </c>
       <c r="F58">
-        <v>101.864</v>
+        <v>103.683</v>
       </c>
       <c r="G58">
         <v>24.5</v>
@@ -6043,28 +6043,28 @@
         <v>28.6</v>
       </c>
       <c r="M58">
-        <v>5.6330792</v>
+        <v>5.7336699</v>
       </c>
       <c r="N58">
-        <v>22.9669208</v>
+        <v>22.8663301</v>
       </c>
       <c r="O58">
-        <v>2.067022872</v>
+        <v>2.057969709</v>
       </c>
       <c r="P58">
-        <v>20.899897928</v>
+        <v>20.808360391</v>
       </c>
       <c r="Q58">
-        <v>26.999897928</v>
+        <v>26.908360391</v>
       </c>
       <c r="R58">
-        <v>1.272727272727273</v>
+        <v>1.325581395348838</v>
       </c>
       <c r="S58">
-        <v>0.1911186993199286</v>
+        <v>0.1943572726330773</v>
       </c>
       <c r="T58">
-        <v>2.114564140554807</v>
+        <v>2.161689328342686</v>
       </c>
       <c r="U58">
         <v>0.0553</v>
@@ -6081,7 +6081,7 @@
         </is>
       </c>
       <c r="Y58">
-        <v>5.077152119572542</v>
+        <v>4.988079275369516</v>
       </c>
       <c r="Z58">
         <v>0</v>
@@ -6089,22 +6089,22 @@
     </row>
     <row r="59">
       <c r="A59">
-        <v>0.5700000000000001</v>
+        <v>0.5800000000000001</v>
       </c>
       <c r="B59">
-        <v>0.1122577372322232</v>
+        <v>0.1122423667636778</v>
       </c>
       <c r="C59">
-        <v>84.45274646882112</v>
+        <v>82.65869060217936</v>
       </c>
       <c r="D59">
-        <v>163.6357464688211</v>
+        <v>163.6606906021794</v>
       </c>
       <c r="E59">
-        <v>71.98299999999999</v>
+        <v>73.80199999999999</v>
       </c>
       <c r="F59">
-        <v>103.683</v>
+        <v>105.502</v>
       </c>
       <c r="G59">
         <v>24.5</v>
@@ -6125,28 +6125,28 @@
         <v>28.6</v>
       </c>
       <c r="M59">
-        <v>5.7336699</v>
+        <v>5.8342606</v>
       </c>
       <c r="N59">
-        <v>22.8663301</v>
+        <v>22.7657394</v>
       </c>
       <c r="O59">
-        <v>2.057969709</v>
+        <v>2.048916546</v>
       </c>
       <c r="P59">
-        <v>20.808360391</v>
+        <v>20.716822854</v>
       </c>
       <c r="Q59">
-        <v>26.908360391</v>
+        <v>26.816822854</v>
       </c>
       <c r="R59">
-        <v>1.325581395348838</v>
+        <v>1.380952380952381</v>
       </c>
       <c r="S59">
-        <v>0.1943572726330773</v>
+        <v>0.1977500637230425</v>
       </c>
       <c r="T59">
-        <v>2.161689328342686</v>
+        <v>2.211058572691892</v>
       </c>
       <c r="U59">
         <v>0.0553</v>
@@ -6163,7 +6163,7 @@
         </is>
       </c>
       <c r="Y59">
-        <v>4.988079275369516</v>
+        <v>4.902077908552799</v>
       </c>
       <c r="Z59">
         <v>0</v>
@@ -6171,22 +6171,22 @@
     </row>
     <row r="60">
       <c r="A60">
-        <v>0.58</v>
+        <v>0.59</v>
       </c>
       <c r="B60">
-        <v>0.1122423667636779</v>
+        <v>0.1122269962951325</v>
       </c>
       <c r="C60">
-        <v>82.65869060217935</v>
+        <v>80.86464234151201</v>
       </c>
       <c r="D60">
-        <v>163.6606906021793</v>
+        <v>163.685642341512</v>
       </c>
       <c r="E60">
-        <v>73.80199999999998</v>
+        <v>75.62099999999998</v>
       </c>
       <c r="F60">
-        <v>105.502</v>
+        <v>107.321</v>
       </c>
       <c r="G60">
         <v>24.5</v>
@@ -6207,28 +6207,28 @@
         <v>28.6</v>
       </c>
       <c r="M60">
-        <v>5.834260599999999</v>
+        <v>5.934851299999999</v>
       </c>
       <c r="N60">
-        <v>22.7657394</v>
+        <v>22.6651487</v>
       </c>
       <c r="O60">
-        <v>2.048916546</v>
+        <v>2.039863383</v>
       </c>
       <c r="P60">
-        <v>20.716822854</v>
+        <v>20.625285317</v>
       </c>
       <c r="Q60">
-        <v>26.816822854</v>
+        <v>26.725285317</v>
       </c>
       <c r="R60">
-        <v>1.380952380952381</v>
+        <v>1.439024390243902</v>
       </c>
       <c r="S60">
-        <v>0.1977500637230425</v>
+        <v>0.2013083568173963</v>
       </c>
       <c r="T60">
-        <v>2.211058572691892</v>
+        <v>2.26283607286301</v>
       </c>
       <c r="U60">
         <v>0.0553</v>
@@ -6245,7 +6245,7 @@
         </is>
       </c>
       <c r="Y60">
-        <v>4.902077908552799</v>
+        <v>4.818991842306143</v>
       </c>
       <c r="Z60">
         <v>0</v>
@@ -6253,22 +6253,22 @@
     </row>
     <row r="61">
       <c r="A61">
-        <v>0.59</v>
+        <v>0.6</v>
       </c>
       <c r="B61">
-        <v>0.1122269962951325</v>
+        <v>0.1122116258265871</v>
       </c>
       <c r="C61">
-        <v>80.86464234151201</v>
+        <v>79.07060169029842</v>
       </c>
       <c r="D61">
-        <v>163.685642341512</v>
+        <v>163.7106016902984</v>
       </c>
       <c r="E61">
-        <v>75.62099999999998</v>
+        <v>77.43999999999998</v>
       </c>
       <c r="F61">
-        <v>107.321</v>
+        <v>109.14</v>
       </c>
       <c r="G61">
         <v>24.5</v>
@@ -6289,28 +6289,28 @@
         <v>28.6</v>
       </c>
       <c r="M61">
-        <v>5.934851299999999</v>
+        <v>6.035442</v>
       </c>
       <c r="N61">
-        <v>22.6651487</v>
+        <v>22.564558</v>
       </c>
       <c r="O61">
-        <v>2.039863383</v>
+        <v>2.03081022</v>
       </c>
       <c r="P61">
-        <v>20.625285317</v>
+        <v>20.53374778</v>
       </c>
       <c r="Q61">
-        <v>26.725285317</v>
+        <v>26.63374778</v>
       </c>
       <c r="R61">
-        <v>1.439024390243902</v>
+        <v>1.5</v>
       </c>
       <c r="S61">
-        <v>0.2013083568173963</v>
+        <v>0.2050445645664677</v>
       </c>
       <c r="T61">
-        <v>2.26283607286301</v>
+        <v>2.317202448042684</v>
       </c>
       <c r="U61">
         <v>0.0553</v>
@@ -6327,7 +6327,7 @@
         </is>
       </c>
       <c r="Y61">
-        <v>4.818991842306143</v>
+        <v>4.73867531160104</v>
       </c>
       <c r="Z61">
         <v>0</v>
@@ -6335,22 +6335,22 @@
     </row>
     <row r="62">
       <c r="A62">
-        <v>0.6</v>
+        <v>0.61</v>
       </c>
       <c r="B62">
-        <v>0.1122116258265871</v>
+        <v>0.1121962553580417</v>
       </c>
       <c r="C62">
-        <v>79.07060169029842</v>
+        <v>77.27656865202009</v>
       </c>
       <c r="D62">
-        <v>163.7106016902984</v>
+        <v>163.7355686520201</v>
       </c>
       <c r="E62">
-        <v>77.43999999999998</v>
+        <v>79.25899999999999</v>
       </c>
       <c r="F62">
-        <v>109.14</v>
+        <v>110.959</v>
       </c>
       <c r="G62">
         <v>24.5</v>
@@ -6371,28 +6371,28 @@
         <v>28.6</v>
       </c>
       <c r="M62">
-        <v>6.035442</v>
+        <v>6.136032699999999</v>
       </c>
       <c r="N62">
-        <v>22.564558</v>
+        <v>22.4639673</v>
       </c>
       <c r="O62">
-        <v>2.03081022</v>
+        <v>2.021757057</v>
       </c>
       <c r="P62">
-        <v>20.53374778</v>
+        <v>20.442210243</v>
       </c>
       <c r="Q62">
-        <v>26.63374778</v>
+        <v>26.542210243</v>
       </c>
       <c r="R62">
-        <v>1.5</v>
+        <v>1.564102564102564</v>
       </c>
       <c r="S62">
-        <v>0.2050445645664677</v>
+        <v>0.2089723727129275</v>
       </c>
       <c r="T62">
-        <v>2.317202448042684</v>
+        <v>2.374356842462342</v>
       </c>
       <c r="U62">
         <v>0.0553</v>
@@ -6409,7 +6409,7 @@
         </is>
       </c>
       <c r="Y62">
-        <v>4.73867531160104</v>
+        <v>4.660992109771515</v>
       </c>
       <c r="Z62">
         <v>0</v>
@@ -6417,22 +6417,22 @@
     </row>
     <row r="63">
       <c r="A63">
-        <v>0.61</v>
+        <v>0.62</v>
       </c>
       <c r="B63">
-        <v>0.1121962553580417</v>
+        <v>0.1121808848894963</v>
       </c>
       <c r="C63">
-        <v>77.27656865202009</v>
+        <v>75.48254323016062</v>
       </c>
       <c r="D63">
-        <v>163.7355686520201</v>
+        <v>163.7605432301606</v>
       </c>
       <c r="E63">
-        <v>79.25899999999999</v>
+        <v>81.07799999999999</v>
       </c>
       <c r="F63">
-        <v>110.959</v>
+        <v>112.778</v>
       </c>
       <c r="G63">
         <v>24.5</v>
@@ -6453,28 +6453,28 @@
         <v>28.6</v>
       </c>
       <c r="M63">
-        <v>6.136032699999999</v>
+        <v>6.2366234</v>
       </c>
       <c r="N63">
-        <v>22.4639673</v>
+        <v>22.3633766</v>
       </c>
       <c r="O63">
-        <v>2.021757057</v>
+        <v>2.012703894</v>
       </c>
       <c r="P63">
-        <v>20.442210243</v>
+        <v>20.350672706</v>
       </c>
       <c r="Q63">
-        <v>26.542210243</v>
+        <v>26.450672706</v>
       </c>
       <c r="R63">
-        <v>1.564102564102564</v>
+        <v>1.631578947368421</v>
       </c>
       <c r="S63">
-        <v>0.2089723727129275</v>
+        <v>0.2131069076039377</v>
       </c>
       <c r="T63">
-        <v>2.374356842462342</v>
+        <v>2.434519362904086</v>
       </c>
       <c r="U63">
         <v>0.0553</v>
@@ -6491,7 +6491,7 @@
         </is>
       </c>
       <c r="Y63">
-        <v>4.660992109771515</v>
+        <v>4.585814817678425</v>
       </c>
       <c r="Z63">
         <v>0</v>
@@ -6499,22 +6499,22 @@
     </row>
     <row r="64">
       <c r="A64">
-        <v>0.62</v>
+        <v>0.63</v>
       </c>
       <c r="B64">
-        <v>0.1121808848894963</v>
+        <v>0.112165514420951</v>
       </c>
       <c r="C64">
-        <v>75.48254323016062</v>
+        <v>73.68852542820576</v>
       </c>
       <c r="D64">
-        <v>163.7605432301606</v>
+        <v>163.7855254282057</v>
       </c>
       <c r="E64">
-        <v>81.07799999999999</v>
+        <v>82.89699999999998</v>
       </c>
       <c r="F64">
-        <v>112.778</v>
+        <v>114.597</v>
       </c>
       <c r="G64">
         <v>24.5</v>
@@ -6535,28 +6535,28 @@
         <v>28.6</v>
       </c>
       <c r="M64">
-        <v>6.2366234</v>
+        <v>6.337214099999999</v>
       </c>
       <c r="N64">
-        <v>22.3633766</v>
+        <v>22.2627859</v>
       </c>
       <c r="O64">
-        <v>2.012703894</v>
+        <v>2.003650731</v>
       </c>
       <c r="P64">
-        <v>20.350672706</v>
+        <v>20.259135169</v>
       </c>
       <c r="Q64">
-        <v>26.450672706</v>
+        <v>26.35913516900001</v>
       </c>
       <c r="R64">
-        <v>1.631578947368421</v>
+        <v>1.702702702702703</v>
       </c>
       <c r="S64">
-        <v>0.2131069076039377</v>
+        <v>0.217464930867435</v>
       </c>
       <c r="T64">
-        <v>2.434519362904086</v>
+        <v>2.497933911477817</v>
       </c>
       <c r="U64">
         <v>0.0553</v>
@@ -6573,7 +6573,7 @@
         </is>
       </c>
       <c r="Y64">
-        <v>4.585814817678425</v>
+        <v>4.513024106286705</v>
       </c>
       <c r="Z64">
         <v>0</v>
@@ -6581,22 +6581,22 @@
     </row>
     <row r="65">
       <c r="A65">
-        <v>0.63</v>
+        <v>0.64</v>
       </c>
       <c r="B65">
-        <v>0.112165514420951</v>
+        <v>0.1136061439524056</v>
       </c>
       <c r="C65">
-        <v>73.68852542820576</v>
+        <v>69.56067194958216</v>
       </c>
       <c r="D65">
-        <v>163.7855254282057</v>
+        <v>161.4766719495821</v>
       </c>
       <c r="E65">
-        <v>82.89699999999998</v>
+        <v>84.71599999999998</v>
       </c>
       <c r="F65">
-        <v>114.597</v>
+        <v>116.416</v>
       </c>
       <c r="G65">
         <v>24.5</v>
@@ -6617,45 +6617,45 @@
         <v>28.6</v>
       </c>
       <c r="M65">
-        <v>6.337214099999999</v>
+        <v>6.728844799999999</v>
       </c>
       <c r="N65">
-        <v>22.2627859</v>
+        <v>21.8711552</v>
       </c>
       <c r="O65">
-        <v>2.003650731</v>
+        <v>1.968403968</v>
       </c>
       <c r="P65">
-        <v>20.259135169</v>
+        <v>19.902751232</v>
       </c>
       <c r="Q65">
-        <v>26.35913516900001</v>
+        <v>26.002751232</v>
       </c>
       <c r="R65">
-        <v>1.702702702702703</v>
+        <v>1.777777777777778</v>
       </c>
       <c r="S65">
-        <v>0.217464930867435</v>
+        <v>0.22206506653446</v>
       </c>
       <c r="T65">
-        <v>2.497933911477817</v>
+        <v>2.564871490527867</v>
       </c>
       <c r="U65">
-        <v>0.0553</v>
+        <v>0.0578</v>
       </c>
       <c r="V65">
         <v>0.09</v>
       </c>
       <c r="W65">
-        <v>0.05032300000000001</v>
+        <v>0.05259800000000001</v>
       </c>
       <c r="X65" t="inlineStr">
         <is>
-          <t>A3/A-</t>
+          <t>Baa2/BBB</t>
         </is>
       </c>
       <c r="Y65">
-        <v>4.513024106286705</v>
+        <v>4.25035810010063</v>
       </c>
       <c r="Z65">
         <v>0</v>
@@ -6663,22 +6663,22 @@
     </row>
     <row r="66">
       <c r="A66">
-        <v>0.64</v>
+        <v>0.65</v>
       </c>
       <c r="B66">
-        <v>0.1136061439524056</v>
+        <v>0.1136135234838602</v>
       </c>
       <c r="C66">
-        <v>69.56067194958216</v>
+        <v>67.73001256142783</v>
       </c>
       <c r="D66">
-        <v>161.4766719495821</v>
+        <v>161.4650125614278</v>
       </c>
       <c r="E66">
-        <v>84.71599999999998</v>
+        <v>86.53499999999998</v>
       </c>
       <c r="F66">
-        <v>116.416</v>
+        <v>118.235</v>
       </c>
       <c r="G66">
         <v>24.5</v>
@@ -6699,28 +6699,28 @@
         <v>28.6</v>
       </c>
       <c r="M66">
-        <v>6.728844799999999</v>
+        <v>6.833983</v>
       </c>
       <c r="N66">
-        <v>21.8711552</v>
+        <v>21.766017</v>
       </c>
       <c r="O66">
-        <v>1.968403968</v>
+        <v>1.95894153</v>
       </c>
       <c r="P66">
-        <v>19.902751232</v>
+        <v>19.80707547</v>
       </c>
       <c r="Q66">
-        <v>26.002751232</v>
+        <v>25.90707547</v>
       </c>
       <c r="R66">
-        <v>1.777777777777778</v>
+        <v>1.857142857142857</v>
       </c>
       <c r="S66">
-        <v>0.22206506653446</v>
+        <v>0.2269280670967434</v>
       </c>
       <c r="T66">
-        <v>2.564871490527867</v>
+        <v>2.635634074095062</v>
       </c>
       <c r="U66">
         <v>0.0578</v>
@@ -6737,7 +6737,7 @@
         </is>
       </c>
       <c r="Y66">
-        <v>4.25035810010063</v>
+        <v>4.184967975483697</v>
       </c>
       <c r="Z66">
         <v>0</v>
@@ -6745,22 +6745,22 @@
     </row>
     <row r="67">
       <c r="A67">
-        <v>0.65</v>
+        <v>0.66</v>
       </c>
       <c r="B67">
-        <v>0.1136135234838602</v>
+        <v>0.1136209030153148</v>
       </c>
       <c r="C67">
-        <v>67.73001256142783</v>
+        <v>65.8993548568791</v>
       </c>
       <c r="D67">
-        <v>161.4650125614278</v>
+        <v>161.4533548568791</v>
       </c>
       <c r="E67">
-        <v>86.53499999999998</v>
+        <v>88.35399999999998</v>
       </c>
       <c r="F67">
-        <v>118.235</v>
+        <v>120.054</v>
       </c>
       <c r="G67">
         <v>24.5</v>
@@ -6781,28 +6781,28 @@
         <v>28.6</v>
       </c>
       <c r="M67">
-        <v>6.833983</v>
+        <v>6.9391212</v>
       </c>
       <c r="N67">
-        <v>21.766017</v>
+        <v>21.6608788</v>
       </c>
       <c r="O67">
-        <v>1.95894153</v>
+        <v>1.949479092</v>
       </c>
       <c r="P67">
-        <v>19.80707547</v>
+        <v>19.711399708</v>
       </c>
       <c r="Q67">
-        <v>25.90707547</v>
+        <v>25.811399708</v>
       </c>
       <c r="R67">
-        <v>1.857142857142857</v>
+        <v>1.941176470588236</v>
       </c>
       <c r="S67">
-        <v>0.2269280670967434</v>
+        <v>0.2320771265156318</v>
       </c>
       <c r="T67">
-        <v>2.635634074095062</v>
+        <v>2.710559162577974</v>
       </c>
       <c r="U67">
         <v>0.0578</v>
@@ -6819,7 +6819,7 @@
         </is>
       </c>
       <c r="Y67">
-        <v>4.184967975483697</v>
+        <v>4.12155936979455</v>
       </c>
       <c r="Z67">
         <v>0</v>
@@ -6827,22 +6827,22 @@
     </row>
     <row r="68">
       <c r="A68">
-        <v>0.66</v>
+        <v>0.67</v>
       </c>
       <c r="B68">
-        <v>0.1136209030153148</v>
+        <v>0.1136282825467694</v>
       </c>
       <c r="C68">
-        <v>65.8993548568791</v>
+        <v>64.06869883557133</v>
       </c>
       <c r="D68">
-        <v>161.4533548568791</v>
+        <v>161.4416988355713</v>
       </c>
       <c r="E68">
-        <v>88.35399999999998</v>
+        <v>90.17299999999999</v>
       </c>
       <c r="F68">
-        <v>120.054</v>
+        <v>121.873</v>
       </c>
       <c r="G68">
         <v>24.5</v>
@@ -6863,28 +6863,28 @@
         <v>28.6</v>
       </c>
       <c r="M68">
-        <v>6.9391212</v>
+        <v>7.0442594</v>
       </c>
       <c r="N68">
-        <v>21.6608788</v>
+        <v>21.5557406</v>
       </c>
       <c r="O68">
-        <v>1.949479092</v>
+        <v>1.940016654</v>
       </c>
       <c r="P68">
-        <v>19.711399708</v>
+        <v>19.615723946</v>
       </c>
       <c r="Q68">
-        <v>25.811399708</v>
+        <v>25.715723946</v>
       </c>
       <c r="R68">
-        <v>1.941176470588236</v>
+        <v>2.030303030303031</v>
       </c>
       <c r="S68">
-        <v>0.2320771265156318</v>
+        <v>0.2375382501417256</v>
       </c>
       <c r="T68">
-        <v>2.710559162577974</v>
+        <v>2.790025165514396</v>
       </c>
       <c r="U68">
         <v>0.0578</v>
@@ -6901,7 +6901,7 @@
         </is>
       </c>
       <c r="Y68">
-        <v>4.12155936979455</v>
+        <v>4.060043558305079</v>
       </c>
       <c r="Z68">
         <v>0</v>
@@ -6909,22 +6909,22 @@
     </row>
     <row r="69">
       <c r="A69">
-        <v>0.67</v>
+        <v>0.68</v>
       </c>
       <c r="B69">
-        <v>0.1136282825467694</v>
+        <v>0.1136356620782241</v>
       </c>
       <c r="C69">
-        <v>64.06869883557133</v>
+        <v>62.23804449714005</v>
       </c>
       <c r="D69">
-        <v>161.4416988355713</v>
+        <v>161.43004449714</v>
       </c>
       <c r="E69">
-        <v>90.17299999999999</v>
+        <v>91.99199999999999</v>
       </c>
       <c r="F69">
-        <v>121.873</v>
+        <v>123.692</v>
       </c>
       <c r="G69">
         <v>24.5</v>
@@ -6945,28 +6945,28 @@
         <v>28.6</v>
       </c>
       <c r="M69">
-        <v>7.0442594</v>
+        <v>7.1493976</v>
       </c>
       <c r="N69">
-        <v>21.5557406</v>
+        <v>21.4506024</v>
       </c>
       <c r="O69">
-        <v>1.940016654</v>
+        <v>1.930554216</v>
       </c>
       <c r="P69">
-        <v>19.615723946</v>
+        <v>19.520048184</v>
       </c>
       <c r="Q69">
-        <v>25.715723946</v>
+        <v>25.620048184</v>
       </c>
       <c r="R69">
-        <v>2.030303030303031</v>
+        <v>2.125</v>
       </c>
       <c r="S69">
-        <v>0.2375382501417256</v>
+        <v>0.2433406939944502</v>
       </c>
       <c r="T69">
-        <v>2.790025165514396</v>
+        <v>2.874457793634345</v>
       </c>
       <c r="U69">
         <v>0.0578</v>
@@ -6983,7 +6983,7 @@
         </is>
       </c>
       <c r="Y69">
-        <v>4.060043558305079</v>
+        <v>4.000337035388828</v>
       </c>
       <c r="Z69">
         <v>0</v>
@@ -6991,22 +6991,22 @@
     </row>
     <row r="70">
       <c r="A70">
-        <v>0.68</v>
+        <v>0.6900000000000001</v>
       </c>
       <c r="B70">
-        <v>0.1136356620782241</v>
+        <v>0.1158406916096787</v>
       </c>
       <c r="C70">
-        <v>62.23804449714005</v>
+        <v>57.0104635791634</v>
       </c>
       <c r="D70">
-        <v>161.43004449714</v>
+        <v>158.0214635791634</v>
       </c>
       <c r="E70">
-        <v>91.99199999999999</v>
+        <v>93.81099999999999</v>
       </c>
       <c r="F70">
-        <v>123.692</v>
+        <v>125.511</v>
       </c>
       <c r="G70">
         <v>24.5</v>
@@ -7027,45 +7027,45 @@
         <v>28.6</v>
       </c>
       <c r="M70">
-        <v>7.1493976</v>
+        <v>7.6938243</v>
       </c>
       <c r="N70">
-        <v>21.4506024</v>
+        <v>20.9061757</v>
       </c>
       <c r="O70">
-        <v>1.930554216</v>
+        <v>1.881555813</v>
       </c>
       <c r="P70">
-        <v>19.520048184</v>
+        <v>19.024619887</v>
       </c>
       <c r="Q70">
-        <v>25.620048184</v>
+        <v>25.12461988700001</v>
       </c>
       <c r="R70">
-        <v>2.125</v>
+        <v>2.225806451612904</v>
       </c>
       <c r="S70">
-        <v>0.2433406939944502</v>
+        <v>0.2495174890634796</v>
       </c>
       <c r="T70">
-        <v>2.874457793634345</v>
+        <v>2.964337688084613</v>
       </c>
       <c r="U70">
-        <v>0.0578</v>
+        <v>0.0613</v>
       </c>
       <c r="V70">
         <v>0.09</v>
       </c>
       <c r="W70">
-        <v>0.05259800000000001</v>
+        <v>0.055783</v>
       </c>
       <c r="X70" t="inlineStr">
         <is>
-          <t>Baa2/BBB</t>
+          <t>Ba1/BB+</t>
         </is>
       </c>
       <c r="Y70">
-        <v>4.000337035388828</v>
+        <v>3.717267107334385</v>
       </c>
       <c r="Z70">
         <v>0</v>
@@ -7073,22 +7073,22 @@
     </row>
     <row r="71">
       <c r="A71">
-        <v>0.6900000000000001</v>
+        <v>0.7000000000000001</v>
       </c>
       <c r="B71">
-        <v>0.1158406916096787</v>
+        <v>0.1158799211411333</v>
       </c>
       <c r="C71">
-        <v>57.0104635791634</v>
+        <v>55.13212448411547</v>
       </c>
       <c r="D71">
-        <v>158.0214635791634</v>
+        <v>157.9621244841155</v>
       </c>
       <c r="E71">
-        <v>93.81099999999999</v>
+        <v>95.63</v>
       </c>
       <c r="F71">
-        <v>125.511</v>
+        <v>127.33</v>
       </c>
       <c r="G71">
         <v>24.5</v>
@@ -7109,28 +7109,28 @@
         <v>28.6</v>
       </c>
       <c r="M71">
-        <v>7.6938243</v>
+        <v>7.805329</v>
       </c>
       <c r="N71">
-        <v>20.9061757</v>
+        <v>20.794671</v>
       </c>
       <c r="O71">
-        <v>1.881555813</v>
+        <v>1.87152039</v>
       </c>
       <c r="P71">
-        <v>19.024619887</v>
+        <v>18.92315061</v>
       </c>
       <c r="Q71">
-        <v>25.12461988700001</v>
+        <v>25.02315061</v>
       </c>
       <c r="R71">
-        <v>2.225806451612904</v>
+        <v>2.333333333333334</v>
       </c>
       <c r="S71">
-        <v>0.2495174890634796</v>
+        <v>0.2561060704704444</v>
       </c>
       <c r="T71">
-        <v>2.964337688084613</v>
+        <v>3.060209575498232</v>
       </c>
       <c r="U71">
         <v>0.0613</v>
@@ -7147,7 +7147,7 @@
         </is>
       </c>
       <c r="Y71">
-        <v>3.717267107334385</v>
+        <v>3.664163291515323</v>
       </c>
       <c r="Z71">
         <v>0</v>
@@ -7155,22 +7155,22 @@
     </row>
     <row r="72">
       <c r="A72">
-        <v>0.7000000000000001</v>
+        <v>0.7100000000000001</v>
       </c>
       <c r="B72">
-        <v>0.1158799211411333</v>
+        <v>0.1159191506725879</v>
       </c>
       <c r="C72">
-        <v>55.13212448411547</v>
+        <v>53.25382993752802</v>
       </c>
       <c r="D72">
-        <v>157.9621244841155</v>
+        <v>157.902829937528</v>
       </c>
       <c r="E72">
-        <v>95.63</v>
+        <v>97.449</v>
       </c>
       <c r="F72">
-        <v>127.33</v>
+        <v>129.149</v>
       </c>
       <c r="G72">
         <v>24.5</v>
@@ -7191,28 +7191,28 @@
         <v>28.6</v>
       </c>
       <c r="M72">
-        <v>7.805329</v>
+        <v>7.9168337</v>
       </c>
       <c r="N72">
-        <v>20.794671</v>
+        <v>20.6831663</v>
       </c>
       <c r="O72">
-        <v>1.87152039</v>
+        <v>1.861484967</v>
       </c>
       <c r="P72">
-        <v>18.92315061</v>
+        <v>18.821681333</v>
       </c>
       <c r="Q72">
-        <v>25.02315061</v>
+        <v>24.92168133300001</v>
       </c>
       <c r="R72">
-        <v>2.333333333333334</v>
+        <v>2.448275862068967</v>
       </c>
       <c r="S72">
-        <v>0.2561060704704444</v>
+        <v>0.2631490368020274</v>
       </c>
       <c r="T72">
-        <v>3.060209575498232</v>
+        <v>3.162693317216239</v>
       </c>
       <c r="U72">
         <v>0.0613</v>
@@ -7229,7 +7229,7 @@
         </is>
       </c>
       <c r="Y72">
-        <v>3.664163291515323</v>
+        <v>3.612555357832008</v>
       </c>
       <c r="Z72">
         <v>0</v>
@@ -7237,22 +7237,22 @@
     </row>
     <row r="73">
       <c r="A73">
-        <v>0.71</v>
+        <v>0.72</v>
       </c>
       <c r="B73">
-        <v>0.1159191506725879</v>
+        <v>0.1159583802040425</v>
       </c>
       <c r="C73">
-        <v>53.25382993752808</v>
+        <v>51.37557988925334</v>
       </c>
       <c r="D73">
-        <v>157.9028299375281</v>
+        <v>157.8435798892533</v>
       </c>
       <c r="E73">
-        <v>97.44899999999997</v>
+        <v>99.26799999999999</v>
       </c>
       <c r="F73">
-        <v>129.149</v>
+        <v>130.968</v>
       </c>
       <c r="G73">
         <v>24.5</v>
@@ -7273,28 +7273,28 @@
         <v>28.6</v>
       </c>
       <c r="M73">
-        <v>7.916833699999998</v>
+        <v>8.028338399999999</v>
       </c>
       <c r="N73">
-        <v>20.6831663</v>
+        <v>20.5716616</v>
       </c>
       <c r="O73">
-        <v>1.861484967</v>
+        <v>1.851449544</v>
       </c>
       <c r="P73">
-        <v>18.821681333</v>
+        <v>18.720212056</v>
       </c>
       <c r="Q73">
-        <v>24.92168133300001</v>
+        <v>24.820212056</v>
       </c>
       <c r="R73">
-        <v>2.448275862068965</v>
+        <v>2.571428571428571</v>
       </c>
       <c r="S73">
-        <v>0.2631490368020273</v>
+        <v>0.2706950721572948</v>
       </c>
       <c r="T73">
-        <v>3.162693317216237</v>
+        <v>3.272497326199816</v>
       </c>
       <c r="U73">
         <v>0.0613</v>
@@ -7311,7 +7311,7 @@
         </is>
       </c>
       <c r="Y73">
-        <v>3.612555357832009</v>
+        <v>3.562380977862119</v>
       </c>
       <c r="Z73">
         <v>0</v>
@@ -7319,22 +7319,22 @@
     </row>
     <row r="74">
       <c r="A74">
-        <v>0.72</v>
+        <v>0.73</v>
       </c>
       <c r="B74">
-        <v>0.1159583802040425</v>
+        <v>0.1159976097354971</v>
       </c>
       <c r="C74">
-        <v>51.37557988925334</v>
+        <v>49.49737428921861</v>
       </c>
       <c r="D74">
-        <v>157.8435798892533</v>
+        <v>157.7843742892186</v>
       </c>
       <c r="E74">
-        <v>99.26799999999999</v>
+        <v>101.087</v>
       </c>
       <c r="F74">
-        <v>130.968</v>
+        <v>132.787</v>
       </c>
       <c r="G74">
         <v>24.5</v>
@@ -7355,28 +7355,28 @@
         <v>28.6</v>
       </c>
       <c r="M74">
-        <v>8.028338399999999</v>
+        <v>8.139843099999998</v>
       </c>
       <c r="N74">
-        <v>20.5716616</v>
+        <v>20.4601569</v>
       </c>
       <c r="O74">
-        <v>1.851449544</v>
+        <v>1.841414121</v>
       </c>
       <c r="P74">
-        <v>18.720212056</v>
+        <v>18.618742779</v>
       </c>
       <c r="Q74">
-        <v>24.820212056</v>
+        <v>24.718742779</v>
       </c>
       <c r="R74">
-        <v>2.571428571428571</v>
+        <v>2.703703703703703</v>
       </c>
       <c r="S74">
-        <v>0.2706950721572948</v>
+        <v>0.2788000730944339</v>
       </c>
       <c r="T74">
-        <v>3.272497326199816</v>
+        <v>3.390434965478474</v>
       </c>
       <c r="U74">
         <v>0.0613</v>
@@ -7393,7 +7393,7 @@
         </is>
       </c>
       <c r="Y74">
-        <v>3.562380977862119</v>
+        <v>3.513581238439351</v>
       </c>
       <c r="Z74">
         <v>0</v>
@@ -7401,22 +7401,22 @@
     </row>
     <row r="75">
       <c r="A75">
-        <v>0.73</v>
+        <v>0.74</v>
       </c>
       <c r="B75">
-        <v>0.1159976097354971</v>
+        <v>0.1179223592669518</v>
       </c>
       <c r="C75">
-        <v>49.49737428921861</v>
+        <v>44.8270859529064</v>
       </c>
       <c r="D75">
-        <v>157.7843742892186</v>
+        <v>154.9330859529064</v>
       </c>
       <c r="E75">
-        <v>101.087</v>
+        <v>102.906</v>
       </c>
       <c r="F75">
-        <v>132.787</v>
+        <v>134.606</v>
       </c>
       <c r="G75">
         <v>24.5</v>
@@ -7437,45 +7437,45 @@
         <v>28.6</v>
       </c>
       <c r="M75">
-        <v>8.139843099999998</v>
+        <v>8.6282446</v>
       </c>
       <c r="N75">
-        <v>20.4601569</v>
+        <v>19.9717554</v>
       </c>
       <c r="O75">
-        <v>1.841414121</v>
+        <v>1.797457986</v>
       </c>
       <c r="P75">
-        <v>18.618742779</v>
+        <v>18.174297414</v>
       </c>
       <c r="Q75">
-        <v>24.718742779</v>
+        <v>24.274297414</v>
       </c>
       <c r="R75">
-        <v>2.703703703703703</v>
+        <v>2.846153846153846</v>
       </c>
       <c r="S75">
-        <v>0.2788000730944339</v>
+        <v>0.2875285356421222</v>
       </c>
       <c r="T75">
-        <v>3.390434965478474</v>
+        <v>3.517444730855491</v>
       </c>
       <c r="U75">
-        <v>0.0613</v>
+        <v>0.0641</v>
       </c>
       <c r="V75">
         <v>0.09</v>
       </c>
       <c r="W75">
-        <v>0.055783</v>
+        <v>0.05833100000000001</v>
       </c>
       <c r="X75" t="inlineStr">
         <is>
-          <t>Ba1/BB+</t>
+          <t>Ba2/BB</t>
         </is>
       </c>
       <c r="Y75">
-        <v>3.513581238439351</v>
+        <v>3.314695088732185</v>
       </c>
       <c r="Z75">
         <v>0</v>
@@ -7483,22 +7483,22 @@
     </row>
     <row r="76">
       <c r="A76">
-        <v>0.74</v>
+        <v>0.75</v>
       </c>
       <c r="B76">
-        <v>0.1179223592669518</v>
+        <v>0.1179870687984064</v>
       </c>
       <c r="C76">
-        <v>44.8270859529064</v>
+        <v>42.91401585835163</v>
       </c>
       <c r="D76">
-        <v>154.9330859529064</v>
+        <v>154.8390158583516</v>
       </c>
       <c r="E76">
-        <v>102.906</v>
+        <v>104.725</v>
       </c>
       <c r="F76">
-        <v>134.606</v>
+        <v>136.425</v>
       </c>
       <c r="G76">
         <v>24.5</v>
@@ -7519,28 +7519,28 @@
         <v>28.6</v>
       </c>
       <c r="M76">
-        <v>8.6282446</v>
+        <v>8.744842499999999</v>
       </c>
       <c r="N76">
-        <v>19.9717554</v>
+        <v>19.8551575</v>
       </c>
       <c r="O76">
-        <v>1.797457986</v>
+        <v>1.786964175</v>
       </c>
       <c r="P76">
-        <v>18.174297414</v>
+        <v>18.068193325</v>
       </c>
       <c r="Q76">
-        <v>24.274297414</v>
+        <v>24.168193325</v>
       </c>
       <c r="R76">
-        <v>2.846153846153846</v>
+        <v>3</v>
       </c>
       <c r="S76">
-        <v>0.2875285356421222</v>
+        <v>0.2969552751936256</v>
       </c>
       <c r="T76">
-        <v>3.517444730855491</v>
+        <v>3.654615277462669</v>
       </c>
       <c r="U76">
         <v>0.0641</v>
@@ -7557,7 +7557,7 @@
         </is>
       </c>
       <c r="Y76">
-        <v>3.314695088732185</v>
+        <v>3.270499154215757</v>
       </c>
       <c r="Z76">
         <v>0</v>
@@ -7565,22 +7565,22 @@
     </row>
     <row r="77">
       <c r="A77">
-        <v>0.75</v>
+        <v>0.76</v>
       </c>
       <c r="B77">
-        <v>0.1179870687984064</v>
+        <v>0.118051778329861</v>
       </c>
       <c r="C77">
-        <v>42.91401585835163</v>
+        <v>41.00105992679789</v>
       </c>
       <c r="D77">
-        <v>154.8390158583516</v>
+        <v>154.7450599267979</v>
       </c>
       <c r="E77">
-        <v>104.725</v>
+        <v>106.544</v>
       </c>
       <c r="F77">
-        <v>136.425</v>
+        <v>138.244</v>
       </c>
       <c r="G77">
         <v>24.5</v>
@@ -7601,28 +7601,28 @@
         <v>28.6</v>
       </c>
       <c r="M77">
-        <v>8.744842499999999</v>
+        <v>8.861440399999999</v>
       </c>
       <c r="N77">
-        <v>19.8551575</v>
+        <v>19.7385596</v>
       </c>
       <c r="O77">
-        <v>1.786964175</v>
+        <v>1.776470364</v>
       </c>
       <c r="P77">
-        <v>18.068193325</v>
+        <v>17.962089236</v>
       </c>
       <c r="Q77">
-        <v>24.168193325</v>
+        <v>24.062089236</v>
       </c>
       <c r="R77">
-        <v>3</v>
+        <v>3.166666666666667</v>
       </c>
       <c r="S77">
-        <v>0.2969552751936256</v>
+        <v>0.3071675763744209</v>
       </c>
       <c r="T77">
-        <v>3.654615277462669</v>
+        <v>3.803216702953778</v>
       </c>
       <c r="U77">
         <v>0.0641</v>
@@ -7639,7 +7639,7 @@
         </is>
       </c>
       <c r="Y77">
-        <v>3.270499154215757</v>
+        <v>3.227466270607655</v>
       </c>
       <c r="Z77">
         <v>0</v>
@@ -7647,22 +7647,22 @@
     </row>
     <row r="78">
       <c r="A78">
-        <v>0.76</v>
+        <v>0.77</v>
       </c>
       <c r="B78">
-        <v>0.118051778329861</v>
+        <v>0.1181164878613157</v>
       </c>
       <c r="C78">
-        <v>41.00105992679789</v>
+        <v>39.08821795054968</v>
       </c>
       <c r="D78">
-        <v>154.7450599267979</v>
+        <v>154.6512179505497</v>
       </c>
       <c r="E78">
-        <v>106.544</v>
+        <v>108.363</v>
       </c>
       <c r="F78">
-        <v>138.244</v>
+        <v>140.063</v>
       </c>
       <c r="G78">
         <v>24.5</v>
@@ -7683,28 +7683,28 @@
         <v>28.6</v>
       </c>
       <c r="M78">
-        <v>8.861440399999999</v>
+        <v>8.9780383</v>
       </c>
       <c r="N78">
-        <v>19.7385596</v>
+        <v>19.6219617</v>
       </c>
       <c r="O78">
-        <v>1.776470364</v>
+        <v>1.765976553</v>
       </c>
       <c r="P78">
-        <v>17.962089236</v>
+        <v>17.855985147</v>
       </c>
       <c r="Q78">
-        <v>24.062089236</v>
+        <v>23.955985147</v>
       </c>
       <c r="R78">
-        <v>3.166666666666667</v>
+        <v>3.347826086956522</v>
       </c>
       <c r="S78">
-        <v>0.3071675763744209</v>
+        <v>0.3182679037448507</v>
       </c>
       <c r="T78">
-        <v>3.803216702953778</v>
+        <v>3.964739991531072</v>
       </c>
       <c r="U78">
         <v>0.0641</v>
@@ -7721,7 +7721,7 @@
         </is>
       </c>
       <c r="Y78">
-        <v>3.227466270607655</v>
+        <v>3.185551124236127</v>
       </c>
       <c r="Z78">
         <v>0</v>
@@ -7729,22 +7729,22 @@
     </row>
     <row r="79">
       <c r="A79">
-        <v>0.77</v>
+        <v>0.78</v>
       </c>
       <c r="B79">
-        <v>0.1181164878613157</v>
+        <v>0.1181811973927703</v>
       </c>
       <c r="C79">
-        <v>39.08821795054968</v>
+        <v>37.17548972241519</v>
       </c>
       <c r="D79">
-        <v>154.6512179505497</v>
+        <v>154.5574897224152</v>
       </c>
       <c r="E79">
-        <v>108.363</v>
+        <v>110.182</v>
       </c>
       <c r="F79">
-        <v>140.063</v>
+        <v>141.882</v>
       </c>
       <c r="G79">
         <v>24.5</v>
@@ -7765,28 +7765,28 @@
         <v>28.6</v>
       </c>
       <c r="M79">
-        <v>8.9780383</v>
+        <v>9.094636199999998</v>
       </c>
       <c r="N79">
-        <v>19.6219617</v>
+        <v>19.5053638</v>
       </c>
       <c r="O79">
-        <v>1.765976553</v>
+        <v>1.755482742</v>
       </c>
       <c r="P79">
-        <v>17.855985147</v>
+        <v>17.749881058</v>
       </c>
       <c r="Q79">
-        <v>23.955985147</v>
+        <v>23.849881058</v>
       </c>
       <c r="R79">
-        <v>3.347826086956522</v>
+        <v>3.545454545454546</v>
       </c>
       <c r="S79">
-        <v>0.3182679037448507</v>
+        <v>0.3303773517853195</v>
       </c>
       <c r="T79">
-        <v>3.964739991531072</v>
+        <v>4.140947215433573</v>
       </c>
       <c r="U79">
         <v>0.0641</v>
@@ -7803,7 +7803,7 @@
         </is>
       </c>
       <c r="Y79">
-        <v>3.185551124236127</v>
+        <v>3.144710725207459</v>
       </c>
       <c r="Z79">
         <v>0</v>
@@ -7811,22 +7811,22 @@
     </row>
     <row r="80">
       <c r="A80">
-        <v>0.78</v>
+        <v>0.79</v>
       </c>
       <c r="B80">
-        <v>0.1181811973927703</v>
+        <v>0.1182459069242249</v>
       </c>
       <c r="C80">
-        <v>37.17548972241519</v>
+        <v>35.26287503570433</v>
       </c>
       <c r="D80">
-        <v>154.5574897224152</v>
+        <v>154.4638750357043</v>
       </c>
       <c r="E80">
-        <v>110.182</v>
+        <v>112.001</v>
       </c>
       <c r="F80">
-        <v>141.882</v>
+        <v>143.701</v>
       </c>
       <c r="G80">
         <v>24.5</v>
@@ -7847,28 +7847,28 @@
         <v>28.6</v>
       </c>
       <c r="M80">
-        <v>9.094636199999998</v>
+        <v>9.2112341</v>
       </c>
       <c r="N80">
-        <v>19.5053638</v>
+        <v>19.3887659</v>
       </c>
       <c r="O80">
-        <v>1.755482742</v>
+        <v>1.744988931</v>
       </c>
       <c r="P80">
-        <v>17.749881058</v>
+        <v>17.643776969</v>
       </c>
       <c r="Q80">
-        <v>23.849881058</v>
+        <v>23.743776969</v>
       </c>
       <c r="R80">
-        <v>3.545454545454546</v>
+        <v>3.761904761904763</v>
       </c>
       <c r="S80">
-        <v>0.3303773517853195</v>
+        <v>0.3436400805915472</v>
       </c>
       <c r="T80">
-        <v>4.140947215433573</v>
+        <v>4.333936079707741</v>
       </c>
       <c r="U80">
         <v>0.0641</v>
@@ -7885,7 +7885,7 @@
         </is>
       </c>
       <c r="Y80">
-        <v>3.144710725207459</v>
+        <v>3.104904260331415</v>
       </c>
       <c r="Z80">
         <v>0</v>
@@ -7893,22 +7893,22 @@
     </row>
     <row r="81">
       <c r="A81">
-        <v>0.79</v>
+        <v>0.8</v>
       </c>
       <c r="B81">
-        <v>0.1182459069242249</v>
+        <v>0.1183106164556795</v>
       </c>
       <c r="C81">
-        <v>35.26287503570433</v>
+        <v>33.35037368422778</v>
       </c>
       <c r="D81">
-        <v>154.4638750357043</v>
+        <v>154.3703736842278</v>
       </c>
       <c r="E81">
-        <v>112.001</v>
+        <v>113.82</v>
       </c>
       <c r="F81">
-        <v>143.701</v>
+        <v>145.52</v>
       </c>
       <c r="G81">
         <v>24.5</v>
@@ -7929,28 +7929,28 @@
         <v>28.6</v>
       </c>
       <c r="M81">
-        <v>9.2112341</v>
+        <v>9.327831999999999</v>
       </c>
       <c r="N81">
-        <v>19.3887659</v>
+        <v>19.272168</v>
       </c>
       <c r="O81">
-        <v>1.744988931</v>
+        <v>1.73449512</v>
       </c>
       <c r="P81">
-        <v>17.643776969</v>
+        <v>17.53767288</v>
       </c>
       <c r="Q81">
-        <v>23.743776969</v>
+        <v>23.63767288</v>
       </c>
       <c r="R81">
-        <v>3.761904761904763</v>
+        <v>4.000000000000001</v>
       </c>
       <c r="S81">
-        <v>0.3436400805915472</v>
+        <v>0.3582290822783976</v>
       </c>
       <c r="T81">
-        <v>4.333936079707741</v>
+        <v>4.546223830409326</v>
       </c>
       <c r="U81">
         <v>0.0641</v>
@@ -7967,7 +7967,7 @@
         </is>
       </c>
       <c r="Y81">
-        <v>3.104904260331415</v>
+        <v>3.066092957077272</v>
       </c>
       <c r="Z81">
         <v>0</v>
@@ -7975,22 +7975,22 @@
     </row>
     <row r="82">
       <c r="A82">
-        <v>0.8</v>
+        <v>0.8100000000000001</v>
       </c>
       <c r="B82">
-        <v>0.1183106164556795</v>
+        <v>0.1183753259871341</v>
       </c>
       <c r="C82">
-        <v>33.35037368422778</v>
+        <v>31.43798546229473</v>
       </c>
       <c r="D82">
-        <v>154.3703736842278</v>
+        <v>154.2769854622947</v>
       </c>
       <c r="E82">
-        <v>113.82</v>
+        <v>115.639</v>
       </c>
       <c r="F82">
-        <v>145.52</v>
+        <v>147.339</v>
       </c>
       <c r="G82">
         <v>24.5</v>
@@ -8011,28 +8011,28 @@
         <v>28.6</v>
       </c>
       <c r="M82">
-        <v>9.327831999999999</v>
+        <v>9.444429900000001</v>
       </c>
       <c r="N82">
-        <v>19.272168</v>
+        <v>19.1555701</v>
       </c>
       <c r="O82">
-        <v>1.73449512</v>
+        <v>1.724001309</v>
       </c>
       <c r="P82">
-        <v>17.53767288</v>
+        <v>17.431568791</v>
       </c>
       <c r="Q82">
-        <v>23.63767288</v>
+        <v>23.531568791</v>
       </c>
       <c r="R82">
-        <v>4.000000000000001</v>
+        <v>4.263157894736843</v>
       </c>
       <c r="S82">
-        <v>0.3582290822783976</v>
+        <v>0.3743537683533376</v>
       </c>
       <c r="T82">
-        <v>4.546223830409326</v>
+        <v>4.78085766013213</v>
       </c>
       <c r="U82">
         <v>0.0641</v>
@@ -8049,7 +8049,7 @@
         </is>
       </c>
       <c r="Y82">
-        <v>3.066092957077272</v>
+        <v>3.028239957607181</v>
       </c>
       <c r="Z82">
         <v>0</v>
@@ -8057,22 +8057,22 @@
     </row>
     <row r="83">
       <c r="A83">
-        <v>0.8100000000000001</v>
+        <v>0.8200000000000001</v>
       </c>
       <c r="B83">
-        <v>0.1183753259871341</v>
+        <v>0.1242603955185888</v>
       </c>
       <c r="C83">
-        <v>31.43798546229473</v>
+        <v>21.57349692968208</v>
       </c>
       <c r="D83">
-        <v>154.2769854622947</v>
+        <v>146.2314969296821</v>
       </c>
       <c r="E83">
-        <v>115.639</v>
+        <v>117.458</v>
       </c>
       <c r="F83">
-        <v>147.339</v>
+        <v>149.158</v>
       </c>
       <c r="G83">
         <v>24.5</v>
@@ -8093,45 +8093,45 @@
         <v>28.6</v>
       </c>
       <c r="M83">
-        <v>9.444429900000001</v>
+        <v>10.7244602</v>
       </c>
       <c r="N83">
-        <v>19.1555701</v>
+        <v>17.8755398</v>
       </c>
       <c r="O83">
-        <v>1.724001309</v>
+        <v>1.608798582</v>
       </c>
       <c r="P83">
-        <v>17.431568791</v>
+        <v>16.266741218</v>
       </c>
       <c r="Q83">
-        <v>23.531568791</v>
+        <v>22.366741218</v>
       </c>
       <c r="R83">
-        <v>4.263157894736843</v>
+        <v>4.555555555555557</v>
       </c>
       <c r="S83">
-        <v>0.3743537683533376</v>
+        <v>0.3922700862143821</v>
       </c>
       <c r="T83">
-        <v>4.78085766013213</v>
+        <v>5.041561915379692</v>
       </c>
       <c r="U83">
-        <v>0.0641</v>
+        <v>0.07190000000000001</v>
       </c>
       <c r="V83">
         <v>0.09</v>
       </c>
       <c r="W83">
-        <v>0.05833100000000001</v>
+        <v>0.065429</v>
       </c>
       <c r="X83" t="inlineStr">
         <is>
-          <t>Ba2/BB</t>
+          <t>B1/B+</t>
         </is>
       </c>
       <c r="Y83">
-        <v>3.028239957607181</v>
+        <v>2.666800889428449</v>
       </c>
       <c r="Z83">
         <v>0</v>
@@ -8139,22 +8139,22 @@
     </row>
     <row r="84">
       <c r="A84">
-        <v>0.8200000000000001</v>
+        <v>0.8300000000000001</v>
       </c>
       <c r="B84">
-        <v>0.1242603955185888</v>
+        <v>0.1243960850500434</v>
       </c>
       <c r="C84">
-        <v>21.57349692968208</v>
+        <v>19.57888053070246</v>
       </c>
       <c r="D84">
-        <v>146.2314969296821</v>
+        <v>146.0558805307025</v>
       </c>
       <c r="E84">
-        <v>117.458</v>
+        <v>119.277</v>
       </c>
       <c r="F84">
-        <v>149.158</v>
+        <v>150.977</v>
       </c>
       <c r="G84">
         <v>24.5</v>
@@ -8175,28 +8175,28 @@
         <v>28.6</v>
       </c>
       <c r="M84">
-        <v>10.7244602</v>
+        <v>10.8552463</v>
       </c>
       <c r="N84">
-        <v>17.8755398</v>
+        <v>17.7447537</v>
       </c>
       <c r="O84">
-        <v>1.608798582</v>
+        <v>1.597027833</v>
       </c>
       <c r="P84">
-        <v>16.266741218</v>
+        <v>16.147725867</v>
       </c>
       <c r="Q84">
-        <v>22.366741218</v>
+        <v>22.247725867</v>
       </c>
       <c r="R84">
-        <v>4.555555555555557</v>
+        <v>4.882352941176473</v>
       </c>
       <c r="S84">
-        <v>0.3922700862143821</v>
+        <v>0.4122942061767259</v>
       </c>
       <c r="T84">
-        <v>5.041561915379692</v>
+        <v>5.332937259479906</v>
       </c>
       <c r="U84">
         <v>0.07190000000000001</v>
@@ -8213,7 +8213,7 @@
         </is>
       </c>
       <c r="Y84">
-        <v>2.666800889428449</v>
+        <v>2.634670758230516</v>
       </c>
       <c r="Z84">
         <v>0</v>
@@ -8221,22 +8221,22 @@
     </row>
     <row r="85">
       <c r="A85">
-        <v>0.8300000000000001</v>
+        <v>0.8400000000000001</v>
       </c>
       <c r="B85">
-        <v>0.1243960850500434</v>
+        <v>0.124531774581498</v>
       </c>
       <c r="C85">
-        <v>19.57888053070246</v>
+        <v>17.58468543802269</v>
       </c>
       <c r="D85">
-        <v>146.0558805307025</v>
+        <v>145.8806854380227</v>
       </c>
       <c r="E85">
-        <v>119.277</v>
+        <v>121.096</v>
       </c>
       <c r="F85">
-        <v>150.977</v>
+        <v>152.796</v>
       </c>
       <c r="G85">
         <v>24.5</v>
@@ -8257,28 +8257,28 @@
         <v>28.6</v>
       </c>
       <c r="M85">
-        <v>10.8552463</v>
+        <v>10.9860324</v>
       </c>
       <c r="N85">
-        <v>17.7447537</v>
+        <v>17.6139676</v>
       </c>
       <c r="O85">
-        <v>1.597027833</v>
+        <v>1.585257084</v>
       </c>
       <c r="P85">
-        <v>16.147725867</v>
+        <v>16.028710516</v>
       </c>
       <c r="Q85">
-        <v>22.247725867</v>
+        <v>22.12871051600001</v>
       </c>
       <c r="R85">
-        <v>4.882352941176473</v>
+        <v>5.250000000000004</v>
       </c>
       <c r="S85">
-        <v>0.4122942061767259</v>
+        <v>0.4348213411343627</v>
       </c>
       <c r="T85">
-        <v>5.332937259479906</v>
+        <v>5.66073452159265</v>
       </c>
       <c r="U85">
         <v>0.07190000000000001</v>
@@ -8295,7 +8295,7 @@
         </is>
       </c>
       <c r="Y85">
-        <v>2.634670758230516</v>
+        <v>2.603305630156343</v>
       </c>
       <c r="Z85">
         <v>0</v>
@@ -8303,22 +8303,22 @@
     </row>
     <row r="86">
       <c r="A86">
-        <v>0.84</v>
+        <v>0.85</v>
       </c>
       <c r="B86">
-        <v>0.124531774581498</v>
+        <v>0.1246674641129526</v>
       </c>
       <c r="C86">
-        <v>17.58468543802272</v>
+        <v>15.59091013737913</v>
       </c>
       <c r="D86">
-        <v>145.8806854380227</v>
+        <v>145.7059101373791</v>
       </c>
       <c r="E86">
-        <v>121.096</v>
+        <v>122.915</v>
       </c>
       <c r="F86">
-        <v>152.796</v>
+        <v>154.615</v>
       </c>
       <c r="G86">
         <v>24.5</v>
@@ -8339,28 +8339,28 @@
         <v>28.6</v>
       </c>
       <c r="M86">
-        <v>10.9860324</v>
+        <v>11.1168185</v>
       </c>
       <c r="N86">
-        <v>17.6139676</v>
+        <v>17.4831815</v>
       </c>
       <c r="O86">
-        <v>1.585257084</v>
+        <v>1.573486335</v>
       </c>
       <c r="P86">
-        <v>16.028710516</v>
+        <v>15.909695165</v>
       </c>
       <c r="Q86">
-        <v>22.12871051600001</v>
+        <v>22.009695165</v>
       </c>
       <c r="R86">
-        <v>5.249999999999999</v>
+        <v>5.666666666666666</v>
       </c>
       <c r="S86">
-        <v>0.4348213411343624</v>
+        <v>0.4603520940863507</v>
       </c>
       <c r="T86">
-        <v>5.660734521592645</v>
+        <v>6.032238085320419</v>
       </c>
       <c r="U86">
         <v>0.07190000000000001</v>
@@ -8377,7 +8377,7 @@
         </is>
       </c>
       <c r="Y86">
-        <v>2.603305630156344</v>
+        <v>2.57267850509568</v>
       </c>
       <c r="Z86">
         <v>0</v>
@@ -8385,22 +8385,22 @@
     </row>
     <row r="87">
       <c r="A87">
-        <v>0.85</v>
+        <v>0.86</v>
       </c>
       <c r="B87">
-        <v>0.1246674641129526</v>
+        <v>0.1248031536444072</v>
       </c>
       <c r="C87">
-        <v>15.59091013737913</v>
+        <v>13.59755312175636</v>
       </c>
       <c r="D87">
-        <v>145.7059101373791</v>
+        <v>145.5315531217563</v>
       </c>
       <c r="E87">
-        <v>122.915</v>
+        <v>124.734</v>
       </c>
       <c r="F87">
-        <v>154.615</v>
+        <v>156.434</v>
       </c>
       <c r="G87">
         <v>24.5</v>
@@ -8421,28 +8421,28 @@
         <v>28.6</v>
       </c>
       <c r="M87">
-        <v>11.1168185</v>
+        <v>11.2476046</v>
       </c>
       <c r="N87">
-        <v>17.4831815</v>
+        <v>17.3523954</v>
       </c>
       <c r="O87">
-        <v>1.573486335</v>
+        <v>1.561715586</v>
       </c>
       <c r="P87">
-        <v>15.909695165</v>
+        <v>15.790679814</v>
       </c>
       <c r="Q87">
-        <v>22.009695165</v>
+        <v>21.890679814</v>
       </c>
       <c r="R87">
-        <v>5.666666666666666</v>
+        <v>6.142857142857142</v>
       </c>
       <c r="S87">
-        <v>0.4603520940863507</v>
+        <v>0.4895300974600517</v>
       </c>
       <c r="T87">
-        <v>6.032238085320419</v>
+        <v>6.456813586723589</v>
       </c>
       <c r="U87">
         <v>0.07190000000000001</v>
@@ -8459,7 +8459,7 @@
         </is>
       </c>
       <c r="Y87">
-        <v>2.57267850509568</v>
+        <v>2.542763638757358</v>
       </c>
       <c r="Z87">
         <v>0</v>
@@ -8467,22 +8467,22 @@
     </row>
     <row r="88">
       <c r="A88">
-        <v>0.86</v>
+        <v>0.87</v>
       </c>
       <c r="B88">
-        <v>0.1248031536444072</v>
+        <v>0.1249388431758618</v>
       </c>
       <c r="C88">
-        <v>13.59755312175636</v>
+        <v>11.60461289134369</v>
       </c>
       <c r="D88">
-        <v>145.5315531217563</v>
+        <v>145.3576128913437</v>
       </c>
       <c r="E88">
-        <v>124.734</v>
+        <v>126.553</v>
       </c>
       <c r="F88">
-        <v>156.434</v>
+        <v>158.253</v>
       </c>
       <c r="G88">
         <v>24.5</v>
@@ -8503,28 +8503,28 @@
         <v>28.6</v>
       </c>
       <c r="M88">
-        <v>11.2476046</v>
+        <v>11.3783907</v>
       </c>
       <c r="N88">
-        <v>17.3523954</v>
+        <v>17.2216093</v>
       </c>
       <c r="O88">
-        <v>1.561715586</v>
+        <v>1.549944837</v>
       </c>
       <c r="P88">
-        <v>15.790679814</v>
+        <v>15.671664463</v>
       </c>
       <c r="Q88">
-        <v>21.890679814</v>
+        <v>21.771664463</v>
       </c>
       <c r="R88">
-        <v>6.142857142857142</v>
+        <v>6.692307692307692</v>
       </c>
       <c r="S88">
-        <v>0.4895300974600517</v>
+        <v>0.5231970244297066</v>
       </c>
       <c r="T88">
-        <v>6.456813586723589</v>
+        <v>6.946708396034939</v>
       </c>
       <c r="U88">
         <v>0.07190000000000001</v>
@@ -8541,7 +8541,7 @@
         </is>
       </c>
       <c r="Y88">
-        <v>2.542763638757358</v>
+        <v>2.513536470495779</v>
       </c>
       <c r="Z88">
         <v>0</v>
@@ -8549,22 +8549,22 @@
     </row>
     <row r="89">
       <c r="A89">
-        <v>0.87</v>
+        <v>0.88</v>
       </c>
       <c r="B89">
-        <v>0.1249388431758618</v>
+        <v>0.1281976527073165</v>
       </c>
       <c r="C89">
-        <v>11.60461289134369</v>
+        <v>5.729570360008552</v>
       </c>
       <c r="D89">
-        <v>145.3576128913437</v>
+        <v>141.3015703600085</v>
       </c>
       <c r="E89">
-        <v>126.553</v>
+        <v>128.372</v>
       </c>
       <c r="F89">
-        <v>158.253</v>
+        <v>160.072</v>
       </c>
       <c r="G89">
         <v>24.5</v>
@@ -8585,45 +8585,45 @@
         <v>28.6</v>
       </c>
       <c r="M89">
-        <v>11.3783907</v>
+        <v>12.1334576</v>
       </c>
       <c r="N89">
-        <v>17.2216093</v>
+        <v>16.4665424</v>
       </c>
       <c r="O89">
-        <v>1.549944837</v>
+        <v>1.481988816</v>
       </c>
       <c r="P89">
-        <v>15.671664463</v>
+        <v>14.984553584</v>
       </c>
       <c r="Q89">
-        <v>21.771664463</v>
+        <v>21.08455358400001</v>
       </c>
       <c r="R89">
-        <v>6.692307692307692</v>
+        <v>7.333333333333334</v>
       </c>
       <c r="S89">
-        <v>0.5231970244297066</v>
+        <v>0.5624751058943039</v>
       </c>
       <c r="T89">
-        <v>6.946708396034939</v>
+        <v>7.518252340231514</v>
       </c>
       <c r="U89">
-        <v>0.07190000000000001</v>
+        <v>0.07580000000000001</v>
       </c>
       <c r="V89">
         <v>0.09</v>
       </c>
       <c r="W89">
-        <v>0.065429</v>
+        <v>0.06897800000000001</v>
       </c>
       <c r="X89" t="inlineStr">
         <is>
-          <t>B1/B+</t>
+          <t>B2/B</t>
         </is>
       </c>
       <c r="Y89">
-        <v>2.513536470495779</v>
+        <v>2.35711871610282</v>
       </c>
       <c r="Z89">
         <v>0</v>
@@ -8631,22 +8631,22 @@
     </row>
     <row r="90">
       <c r="A90">
-        <v>0.88</v>
+        <v>0.89</v>
       </c>
       <c r="B90">
-        <v>0.1281976527073165</v>
+        <v>0.1283688322387711</v>
       </c>
       <c r="C90">
-        <v>5.729570360008552</v>
+        <v>3.703761822086705</v>
       </c>
       <c r="D90">
-        <v>141.3015703600085</v>
+        <v>141.0947618220867</v>
       </c>
       <c r="E90">
-        <v>128.372</v>
+        <v>130.191</v>
       </c>
       <c r="F90">
-        <v>160.072</v>
+        <v>161.891</v>
       </c>
       <c r="G90">
         <v>24.5</v>
@@ -8667,28 +8667,28 @@
         <v>28.6</v>
       </c>
       <c r="M90">
-        <v>12.1334576</v>
+        <v>12.2713378</v>
       </c>
       <c r="N90">
-        <v>16.4665424</v>
+        <v>16.3286622</v>
       </c>
       <c r="O90">
-        <v>1.481988816</v>
+        <v>1.469579598</v>
       </c>
       <c r="P90">
-        <v>14.984553584</v>
+        <v>14.859082602</v>
       </c>
       <c r="Q90">
-        <v>21.08455358400001</v>
+        <v>20.959082602</v>
       </c>
       <c r="R90">
-        <v>7.333333333333334</v>
+        <v>8.090909090909092</v>
       </c>
       <c r="S90">
-        <v>0.5624751058943039</v>
+        <v>0.608894656716101</v>
       </c>
       <c r="T90">
-        <v>7.518252340231514</v>
+        <v>8.193713365191103</v>
       </c>
       <c r="U90">
         <v>0.07580000000000001</v>
@@ -8705,7 +8705,7 @@
         </is>
       </c>
       <c r="Y90">
-        <v>2.35711871610282</v>
+        <v>2.330634236146609</v>
       </c>
       <c r="Z90">
         <v>0</v>
@@ -8713,22 +8713,22 @@
     </row>
     <row r="91">
       <c r="A91">
-        <v>0.89</v>
+        <v>0.9</v>
       </c>
       <c r="B91">
-        <v>0.1283688322387711</v>
+        <v>0.1285400117702257</v>
       </c>
       <c r="C91">
-        <v>3.703761822086705</v>
+        <v>1.67855776810697</v>
       </c>
       <c r="D91">
-        <v>141.0947618220867</v>
+        <v>140.8885577681069</v>
       </c>
       <c r="E91">
-        <v>130.191</v>
+        <v>132.01</v>
       </c>
       <c r="F91">
-        <v>161.891</v>
+        <v>163.71</v>
       </c>
       <c r="G91">
         <v>24.5</v>
@@ -8749,28 +8749,28 @@
         <v>28.6</v>
       </c>
       <c r="M91">
-        <v>12.2713378</v>
+        <v>12.409218</v>
       </c>
       <c r="N91">
-        <v>16.3286622</v>
+        <v>16.190782</v>
       </c>
       <c r="O91">
-        <v>1.469579598</v>
+        <v>1.45717038</v>
       </c>
       <c r="P91">
-        <v>14.859082602</v>
+        <v>14.73361162</v>
       </c>
       <c r="Q91">
-        <v>20.959082602</v>
+        <v>20.83361162</v>
       </c>
       <c r="R91">
-        <v>8.090909090909092</v>
+        <v>9.000000000000002</v>
       </c>
       <c r="S91">
-        <v>0.608894656716101</v>
+        <v>0.6645981177022572</v>
       </c>
       <c r="T91">
-        <v>8.193713365191103</v>
+        <v>9.004266595142608</v>
       </c>
       <c r="U91">
         <v>0.07580000000000001</v>
@@ -8787,7 +8787,7 @@
         </is>
       </c>
       <c r="Y91">
-        <v>2.330634236146609</v>
+        <v>2.304738300189424</v>
       </c>
       <c r="Z91">
         <v>0</v>
@@ -8795,22 +8795,22 @@
     </row>
     <row r="92">
       <c r="A92">
-        <v>0.9</v>
+        <v>0.91</v>
       </c>
       <c r="B92">
-        <v>0.1285400117702257</v>
+        <v>0.1287111913016803</v>
       </c>
       <c r="C92">
-        <v>1.67855776810697</v>
+        <v>-0.3460444483465608</v>
       </c>
       <c r="D92">
-        <v>140.8885577681069</v>
+        <v>140.6829555516534</v>
       </c>
       <c r="E92">
-        <v>132.01</v>
+        <v>133.829</v>
       </c>
       <c r="F92">
-        <v>163.71</v>
+        <v>165.529</v>
       </c>
       <c r="G92">
         <v>24.5</v>
@@ -8831,28 +8831,28 @@
         <v>28.6</v>
       </c>
       <c r="M92">
-        <v>12.409218</v>
+        <v>12.5470982</v>
       </c>
       <c r="N92">
-        <v>16.190782</v>
+        <v>16.0529018</v>
       </c>
       <c r="O92">
-        <v>1.45717038</v>
+        <v>1.444761162</v>
       </c>
       <c r="P92">
-        <v>14.73361162</v>
+        <v>14.608140638</v>
       </c>
       <c r="Q92">
-        <v>20.83361162</v>
+        <v>20.708140638</v>
       </c>
       <c r="R92">
-        <v>9.000000000000002</v>
+        <v>10.11111111111111</v>
       </c>
       <c r="S92">
-        <v>0.6645981177022572</v>
+        <v>0.7326801255742262</v>
       </c>
       <c r="T92">
-        <v>9.004266595142608</v>
+        <v>9.994942765083341</v>
       </c>
       <c r="U92">
         <v>0.07580000000000001</v>
@@ -8869,7 +8869,7 @@
         </is>
       </c>
       <c r="Y92">
-        <v>2.304738300189424</v>
+        <v>2.279411505681848</v>
       </c>
       <c r="Z92">
         <v>0</v>
@@ -8877,22 +8877,22 @@
     </row>
     <row r="93">
       <c r="A93">
-        <v>0.91</v>
+        <v>0.92</v>
       </c>
       <c r="B93">
-        <v>0.1287111913016803</v>
+        <v>0.128882370833135</v>
       </c>
       <c r="C93">
-        <v>-0.3460444483465608</v>
+        <v>-2.370047458264281</v>
       </c>
       <c r="D93">
-        <v>140.6829555516534</v>
+        <v>140.4779525417357</v>
       </c>
       <c r="E93">
-        <v>133.829</v>
+        <v>135.648</v>
       </c>
       <c r="F93">
-        <v>165.529</v>
+        <v>167.348</v>
       </c>
       <c r="G93">
         <v>24.5</v>
@@ -8913,28 +8913,28 @@
         <v>28.6</v>
       </c>
       <c r="M93">
-        <v>12.5470982</v>
+        <v>12.6849784</v>
       </c>
       <c r="N93">
-        <v>16.0529018</v>
+        <v>15.9150216</v>
       </c>
       <c r="O93">
-        <v>1.444761162</v>
+        <v>1.432351944</v>
       </c>
       <c r="P93">
-        <v>14.608140638</v>
+        <v>14.482669656</v>
       </c>
       <c r="Q93">
-        <v>20.708140638</v>
+        <v>20.582669656</v>
       </c>
       <c r="R93">
-        <v>10.11111111111111</v>
+        <v>11.50000000000001</v>
       </c>
       <c r="S93">
-        <v>0.7326801255742262</v>
+        <v>0.8177826354141875</v>
       </c>
       <c r="T93">
-        <v>9.994942765083341</v>
+        <v>11.23328797750926</v>
       </c>
       <c r="U93">
         <v>0.07580000000000001</v>
@@ -8951,7 +8951,7 @@
         </is>
       </c>
       <c r="Y93">
-        <v>2.279411505681848</v>
+        <v>2.254635293663567</v>
       </c>
       <c r="Z93">
         <v>0</v>
@@ -8959,22 +8959,22 @@
     </row>
     <row r="94">
       <c r="A94">
-        <v>0.92</v>
+        <v>0.93</v>
       </c>
       <c r="B94">
-        <v>0.128882370833135</v>
+        <v>0.1290535503645896</v>
       </c>
       <c r="C94">
-        <v>-2.370047458264281</v>
+        <v>-4.393453877323566</v>
       </c>
       <c r="D94">
-        <v>140.4779525417357</v>
+        <v>140.2735461226764</v>
       </c>
       <c r="E94">
-        <v>135.648</v>
+        <v>137.467</v>
       </c>
       <c r="F94">
-        <v>167.348</v>
+        <v>169.167</v>
       </c>
       <c r="G94">
         <v>24.5</v>
@@ -8995,28 +8995,28 @@
         <v>28.6</v>
       </c>
       <c r="M94">
-        <v>12.6849784</v>
+        <v>12.8228586</v>
       </c>
       <c r="N94">
-        <v>15.9150216</v>
+        <v>15.7771414</v>
       </c>
       <c r="O94">
-        <v>1.432351944</v>
+        <v>1.419942726</v>
       </c>
       <c r="P94">
-        <v>14.482669656</v>
+        <v>14.357198674</v>
       </c>
       <c r="Q94">
-        <v>20.582669656</v>
+        <v>20.457198674</v>
       </c>
       <c r="R94">
-        <v>11.50000000000001</v>
+        <v>13.2857142857143</v>
       </c>
       <c r="S94">
-        <v>0.8177826354141875</v>
+        <v>0.9272001480655661</v>
       </c>
       <c r="T94">
-        <v>11.23328797750926</v>
+        <v>12.82544610777114</v>
       </c>
       <c r="U94">
         <v>0.07580000000000001</v>
@@ -9033,7 +9033,7 @@
         </is>
       </c>
       <c r="Y94">
-        <v>2.254635293663567</v>
+        <v>2.23039190340912</v>
       </c>
       <c r="Z94">
         <v>0</v>
@@ -9041,22 +9041,22 @@
     </row>
     <row r="95">
       <c r="A95">
-        <v>0.93</v>
+        <v>0.9400000000000001</v>
       </c>
       <c r="B95">
-        <v>0.1290535503645896</v>
+        <v>0.1292247298960442</v>
       </c>
       <c r="C95">
-        <v>-4.393453877323566</v>
+        <v>-6.416266305999613</v>
       </c>
       <c r="D95">
-        <v>140.2735461226764</v>
+        <v>140.0697336940004</v>
       </c>
       <c r="E95">
-        <v>137.467</v>
+        <v>139.286</v>
       </c>
       <c r="F95">
-        <v>169.167</v>
+        <v>170.986</v>
       </c>
       <c r="G95">
         <v>24.5</v>
@@ -9077,28 +9077,28 @@
         <v>28.6</v>
       </c>
       <c r="M95">
-        <v>12.8228586</v>
+        <v>12.9607388</v>
       </c>
       <c r="N95">
-        <v>15.7771414</v>
+        <v>15.6392612</v>
       </c>
       <c r="O95">
-        <v>1.419942726</v>
+        <v>1.407533508</v>
       </c>
       <c r="P95">
-        <v>14.357198674</v>
+        <v>14.231727692</v>
       </c>
       <c r="Q95">
-        <v>20.457198674</v>
+        <v>20.331727692</v>
       </c>
       <c r="R95">
-        <v>13.2857142857143</v>
+        <v>15.66666666666668</v>
       </c>
       <c r="S95">
-        <v>0.9272001480655661</v>
+        <v>1.073090164934071</v>
       </c>
       <c r="T95">
-        <v>12.82544610777114</v>
+        <v>14.948323614787</v>
       </c>
       <c r="U95">
         <v>0.07580000000000001</v>
@@ -9115,7 +9115,7 @@
         </is>
       </c>
       <c r="Y95">
-        <v>2.23039190340912</v>
+        <v>2.206664329968597</v>
       </c>
       <c r="Z95">
         <v>0</v>
@@ -9123,22 +9123,22 @@
     </row>
     <row r="96">
       <c r="A96">
-        <v>0.9400000000000001</v>
+        <v>0.9500000000000001</v>
       </c>
       <c r="B96">
-        <v>0.1292247298960442</v>
+        <v>0.1293959094274988</v>
       </c>
       <c r="C96">
-        <v>-6.416266305999613</v>
+        <v>-8.43848732967615</v>
       </c>
       <c r="D96">
-        <v>140.0697336940004</v>
+        <v>139.8665126703238</v>
       </c>
       <c r="E96">
-        <v>139.286</v>
+        <v>141.105</v>
       </c>
       <c r="F96">
-        <v>170.986</v>
+        <v>172.805</v>
       </c>
       <c r="G96">
         <v>24.5</v>
@@ -9159,28 +9159,28 @@
         <v>28.6</v>
       </c>
       <c r="M96">
-        <v>12.9607388</v>
+        <v>13.098619</v>
       </c>
       <c r="N96">
-        <v>15.6392612</v>
+        <v>15.501381</v>
       </c>
       <c r="O96">
-        <v>1.407533508</v>
+        <v>1.39512429</v>
       </c>
       <c r="P96">
-        <v>14.231727692</v>
+        <v>14.10625671</v>
       </c>
       <c r="Q96">
-        <v>20.331727692</v>
+        <v>20.20625671000001</v>
       </c>
       <c r="R96">
-        <v>15.66666666666668</v>
+        <v>19.00000000000003</v>
       </c>
       <c r="S96">
-        <v>1.073090164934071</v>
+        <v>1.277336188549978</v>
       </c>
       <c r="T96">
-        <v>14.948323614787</v>
+        <v>17.9203521246092</v>
       </c>
       <c r="U96">
         <v>0.07580000000000001</v>
@@ -9197,7 +9197,7 @@
         </is>
       </c>
       <c r="Y96">
-        <v>2.206664329968597</v>
+        <v>2.18343628438998</v>
       </c>
       <c r="Z96">
         <v>0</v>
@@ -9205,22 +9205,22 @@
     </row>
     <row r="97">
       <c r="A97">
-        <v>0.9500000000000001</v>
+        <v>0.9600000000000001</v>
       </c>
       <c r="B97">
-        <v>0.1293959094274988</v>
+        <v>0.1295670889589535</v>
       </c>
       <c r="C97">
-        <v>-8.43848732967615</v>
+        <v>-10.46011951875457</v>
       </c>
       <c r="D97">
-        <v>139.8665126703238</v>
+        <v>139.6638804812454</v>
       </c>
       <c r="E97">
-        <v>141.105</v>
+        <v>142.924</v>
       </c>
       <c r="F97">
-        <v>172.805</v>
+        <v>174.624</v>
       </c>
       <c r="G97">
         <v>24.5</v>
@@ -9241,28 +9241,28 @@
         <v>28.6</v>
       </c>
       <c r="M97">
-        <v>13.098619</v>
+        <v>13.2364992</v>
       </c>
       <c r="N97">
-        <v>15.501381</v>
+        <v>15.3635008</v>
       </c>
       <c r="O97">
-        <v>1.39512429</v>
+        <v>1.382715072</v>
       </c>
       <c r="P97">
-        <v>14.10625671</v>
+        <v>13.980785728</v>
       </c>
       <c r="Q97">
-        <v>20.20625671000001</v>
+        <v>20.080785728</v>
       </c>
       <c r="R97">
-        <v>19.00000000000003</v>
+        <v>24.00000000000005</v>
       </c>
       <c r="S97">
-        <v>1.277336188549978</v>
+        <v>1.583705223973839</v>
       </c>
       <c r="T97">
-        <v>17.9203521246092</v>
+        <v>22.37839488934249</v>
       </c>
       <c r="U97">
         <v>0.07580000000000001</v>
@@ -9279,7 +9279,7 @@
         </is>
       </c>
       <c r="Y97">
-        <v>2.18343628438998</v>
+        <v>2.160692156427585</v>
       </c>
       <c r="Z97">
         <v>0</v>
@@ -9287,22 +9287,22 @@
     </row>
     <row r="98">
       <c r="A98">
-        <v>0.96</v>
+        <v>0.97</v>
       </c>
       <c r="B98">
-        <v>0.1295670889589535</v>
+        <v>0.1297382684904081</v>
       </c>
       <c r="C98">
-        <v>-10.46011951875454</v>
+        <v>-12.48116542876207</v>
       </c>
       <c r="D98">
-        <v>139.6638804812454</v>
+        <v>139.4618345712379</v>
       </c>
       <c r="E98">
-        <v>142.924</v>
+        <v>144.743</v>
       </c>
       <c r="F98">
-        <v>174.624</v>
+        <v>176.443</v>
       </c>
       <c r="G98">
         <v>24.5</v>
@@ -9323,28 +9323,28 @@
         <v>28.6</v>
       </c>
       <c r="M98">
-        <v>13.2364992</v>
+        <v>13.3743794</v>
       </c>
       <c r="N98">
-        <v>15.3635008</v>
+        <v>15.2256206</v>
       </c>
       <c r="O98">
-        <v>1.382715072</v>
+        <v>1.370305854</v>
       </c>
       <c r="P98">
-        <v>13.980785728</v>
+        <v>13.855314746</v>
       </c>
       <c r="Q98">
-        <v>20.080785728</v>
+        <v>19.955314746</v>
       </c>
       <c r="R98">
-        <v>23.99999999999998</v>
+        <v>32.33333333333331</v>
       </c>
       <c r="S98">
-        <v>1.583705223973835</v>
+        <v>2.094320283013601</v>
       </c>
       <c r="T98">
-        <v>22.37839488934244</v>
+        <v>29.8084661638979</v>
       </c>
       <c r="U98">
         <v>0.07580000000000001</v>
@@ -9361,7 +9361,7 @@
         </is>
       </c>
       <c r="Y98">
-        <v>2.160692156427585</v>
+        <v>2.138416979557197</v>
       </c>
       <c r="Z98">
         <v>0</v>
@@ -9369,22 +9369,22 @@
     </row>
     <row r="99">
       <c r="A99">
-        <v>0.97</v>
+        <v>0.98</v>
       </c>
       <c r="B99">
-        <v>0.1297382684904081</v>
+        <v>0.1299094480218627</v>
       </c>
       <c r="C99">
-        <v>-12.48116542876207</v>
+        <v>-14.50162760045956</v>
       </c>
       <c r="D99">
-        <v>139.4618345712379</v>
+        <v>139.2603723995404</v>
       </c>
       <c r="E99">
-        <v>144.743</v>
+        <v>146.562</v>
       </c>
       <c r="F99">
-        <v>176.443</v>
+        <v>178.262</v>
       </c>
       <c r="G99">
         <v>24.5</v>
@@ -9405,28 +9405,28 @@
         <v>28.6</v>
       </c>
       <c r="M99">
-        <v>13.3743794</v>
+        <v>13.5122596</v>
       </c>
       <c r="N99">
-        <v>15.2256206</v>
+        <v>15.0877404</v>
       </c>
       <c r="O99">
-        <v>1.370305854</v>
+        <v>1.357896636</v>
       </c>
       <c r="P99">
-        <v>13.855314746</v>
+        <v>13.729843764</v>
       </c>
       <c r="Q99">
-        <v>19.955314746</v>
+        <v>19.829843764</v>
       </c>
       <c r="R99">
-        <v>32.33333333333331</v>
+        <v>48.99999999999996</v>
       </c>
       <c r="S99">
-        <v>2.094320283013601</v>
+        <v>3.115550401093132</v>
       </c>
       <c r="T99">
-        <v>29.8084661638979</v>
+        <v>44.66860871300883</v>
       </c>
       <c r="U99">
         <v>0.07580000000000001</v>
@@ -9443,7 +9443,7 @@
         </is>
       </c>
       <c r="Y99">
-        <v>2.138416979557197</v>
+        <v>2.116596398133145</v>
       </c>
       <c r="Z99">
         <v>0</v>
@@ -9451,22 +9451,22 @@
     </row>
     <row r="100">
       <c r="A100">
-        <v>0.98</v>
+        <v>0.99</v>
       </c>
       <c r="B100">
-        <v>0.1299094480218627</v>
+        <v>0.1300806275533173</v>
       </c>
       <c r="C100">
-        <v>-14.50162760045956</v>
+        <v>-16.52150855994785</v>
       </c>
       <c r="D100">
-        <v>139.2603723995404</v>
+        <v>139.0594914400521</v>
       </c>
       <c r="E100">
-        <v>146.562</v>
+        <v>148.381</v>
       </c>
       <c r="F100">
-        <v>178.262</v>
+        <v>180.081</v>
       </c>
       <c r="G100">
         <v>24.5</v>
@@ -9487,28 +9487,28 @@
         <v>28.6</v>
       </c>
       <c r="M100">
-        <v>13.5122596</v>
+        <v>13.6501398</v>
       </c>
       <c r="N100">
-        <v>15.0877404</v>
+        <v>14.9498602</v>
       </c>
       <c r="O100">
-        <v>1.357896636</v>
+        <v>1.345487418</v>
       </c>
       <c r="P100">
-        <v>13.729843764</v>
+        <v>13.604372782</v>
       </c>
       <c r="Q100">
-        <v>19.829843764</v>
+        <v>19.704372782</v>
       </c>
       <c r="R100">
-        <v>48.99999999999996</v>
+        <v>98.99999999999991</v>
       </c>
       <c r="S100">
-        <v>3.115550401093132</v>
+        <v>6.179240755331726</v>
       </c>
       <c r="T100">
-        <v>44.66860871300883</v>
+        <v>89.24903636034162</v>
       </c>
       <c r="U100">
         <v>0.07580000000000001</v>
@@ -9525,91 +9525,9 @@
         </is>
       </c>
       <c r="Y100">
-        <v>2.116596398133145</v>
+        <v>2.09521663653584</v>
       </c>
       <c r="Z100">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="101">
-      <c r="A101">
-        <v>0.99</v>
-      </c>
-      <c r="B101">
-        <v>0.1300806275533173</v>
-      </c>
-      <c r="C101">
-        <v>-16.52150855994785</v>
-      </c>
-      <c r="D101">
-        <v>139.0594914400521</v>
-      </c>
-      <c r="E101">
-        <v>148.381</v>
-      </c>
-      <c r="F101">
-        <v>180.081</v>
-      </c>
-      <c r="G101">
-        <v>24.5</v>
-      </c>
-      <c r="H101">
-        <v>150.2</v>
-      </c>
-      <c r="I101">
-        <v>0</v>
-      </c>
-      <c r="J101">
-        <v>34.7</v>
-      </c>
-      <c r="K101">
-        <v>6.100000000000001</v>
-      </c>
-      <c r="L101">
-        <v>28.6</v>
-      </c>
-      <c r="M101">
-        <v>13.6501398</v>
-      </c>
-      <c r="N101">
-        <v>14.9498602</v>
-      </c>
-      <c r="O101">
-        <v>1.345487418</v>
-      </c>
-      <c r="P101">
-        <v>13.604372782</v>
-      </c>
-      <c r="Q101">
-        <v>19.704372782</v>
-      </c>
-      <c r="R101">
-        <v>98.99999999999991</v>
-      </c>
-      <c r="S101">
-        <v>6.179240755331726</v>
-      </c>
-      <c r="T101">
-        <v>89.24903636034162</v>
-      </c>
-      <c r="U101">
-        <v>0.07580000000000001</v>
-      </c>
-      <c r="V101">
-        <v>0.09</v>
-      </c>
-      <c r="W101">
-        <v>0.06897800000000001</v>
-      </c>
-      <c r="X101" t="inlineStr">
-        <is>
-          <t>B2/B</t>
-        </is>
-      </c>
-      <c r="Y101">
-        <v>2.09521663653584</v>
-      </c>
-      <c r="Z101">
         <v>0</v>
       </c>
     </row>
